--- a/data/seed/portfolio/L-2025-5488/vypiska_2026-07_09.xlsx
+++ b/data/seed/portfolio/L-2025-5488/vypiska_2026-07_09.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J153"/>
+  <dimension ref="A1:J162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -540,263 +540,263 @@
       <c r="B8" t="n">
         <v>100</v>
       </c>
-      <c r="C8" s="2" t="n"/>
-      <c r="D8" s="2" t="n">
-        <v>6981000</v>
-      </c>
+      <c r="C8" s="2" t="n">
+        <v>37920000</v>
+      </c>
+      <c r="D8" s="2" t="n"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Gulshan Yog' Zavodi MChJ</t>
+          <t>Qarshi Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>317122453</t>
+          <t>242558726</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>20208000340980178001</t>
+          <t>20208000685861603001</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №2/26, QQS 12%</t>
+          <t>Materiallar uchun oldindan to'lov, shartn. №71/26</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>228881000</v>
+        <v>183980000</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B9" t="n">
         <v>101</v>
       </c>
-      <c r="C9" s="2" t="n">
-        <v>3712000</v>
-      </c>
-      <c r="D9" s="2" t="n"/>
+      <c r="C9" s="2" t="n"/>
+      <c r="D9" s="2" t="n">
+        <v>40606000</v>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Durdona Dori-Darmon MChJ</t>
+          <t>Sarbon Agro AJ</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>306318030</t>
+          <t>230167378</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>20208000554383246001</t>
+          <t>20208000670005672001</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №80/26</t>
+          <t>Shartnoma №258/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>225169000</v>
+        <v>224586000</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B10" t="n">
         <v>102</v>
       </c>
-      <c r="C10" s="2" t="n">
-        <v>6211000</v>
-      </c>
-      <c r="D10" s="2" t="n"/>
+      <c r="C10" s="2" t="n"/>
+      <c r="D10" s="2" t="n">
+        <v>4808000</v>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Namangan Sut Mahsulotlari MChJ</t>
+          <t>Xiva Polimer AJ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>231235630</t>
+          <t>257873684</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20208000785568112001</t>
+          <t>20208000626499181001</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №83/26 от 01.07.2026, НДС 12%</t>
+          <t>Tovar uchun to'lov, hisob-faktura №6044 02.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>218958000</v>
+        <v>229394000</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>46206</v>
+        <v>46205</v>
       </c>
       <c r="B11" t="n">
         <v>103</v>
       </c>
-      <c r="C11" s="2" t="n"/>
-      <c r="D11" s="2" t="n">
-        <v>10380000</v>
-      </c>
+      <c r="C11" s="2" t="n">
+        <v>2738000</v>
+      </c>
+      <c r="D11" s="2" t="n"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Jizzax Non AJ</t>
+          <t>Andijon Logistik MChJ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>384578736</t>
+          <t>290703257</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>20208000406264991001</t>
+          <t>20208000232420108001</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №8766 03.07.2026, QQS bilan</t>
+          <t>Предоплата за материалы по договору №289/26</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>229338000</v>
+        <v>226656000</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>46206</v>
+        <v>46205</v>
       </c>
       <c r="B12" t="n">
         <v>104</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>9898000</v>
+        <v>3505000</v>
       </c>
       <c r="D12" s="2" t="n"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Zafar Trans Servis XK</t>
+          <t>Nurafshon Logistik XK</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>350425587</t>
+          <t>267357497</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20208000646858616001</t>
+          <t>20208000958282772001</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №1580</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №266/26</t>
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>219440000</v>
+        <v>223151000</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>46209</v>
+        <v>46205</v>
       </c>
       <c r="B13" t="n">
         <v>105</v>
       </c>
-      <c r="C13" s="2" t="n"/>
-      <c r="D13" s="2" t="n">
-        <v>25125000</v>
-      </c>
+      <c r="C13" s="2" t="n">
+        <v>18054000</v>
+      </c>
+      <c r="D13" s="2" t="n"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Jizzax Non AJ</t>
+          <t>Nurafshon Moy MChJ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>384578736</t>
+          <t>331803035</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>20208000406264991001</t>
+          <t>20208000438324655001</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №1871</t>
+          <t>Tovarlar uchun to'lov h/f №674</t>
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>244565000</v>
+        <v>205097000</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>46209</v>
+        <v>46206</v>
       </c>
       <c r="B14" t="n">
         <v>106</v>
       </c>
-      <c r="C14" s="2" t="n"/>
-      <c r="D14" s="2" t="n">
-        <v>11147000</v>
-      </c>
+      <c r="C14" s="2" t="n">
+        <v>9368000</v>
+      </c>
+      <c r="D14" s="2" t="n"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Jizzax Non AJ</t>
+          <t>Nurafshon Logistik XK</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>384578736</t>
+          <t>267357497</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20208000406264991001</t>
+          <t>20208000958282772001</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -806,11 +806,11 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №116/26, QQS 12%</t>
+          <t>XOM ASHYO UCHUN TO'LOV, SHARTNOMA №27/26, QQS BILAN</t>
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>255712000</v>
+        <v>195729000</v>
       </c>
     </row>
     <row r="15">
@@ -822,35 +822,35 @@
       </c>
       <c r="C15" s="2" t="n"/>
       <c r="D15" s="2" t="n">
-        <v>9938000</v>
+        <v>14357000</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Gulshan Yog' Zavodi MChJ</t>
+          <t>Xiva Polimer AJ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>317122453</t>
+          <t>257873684</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>20208000340980178001</t>
+          <t>20208000626499181001</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Shartnoma №144/26 bo'yicha oldindan to'lov</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №870</t>
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>265650000</v>
+        <v>210086000</v>
       </c>
     </row>
     <row r="16">
@@ -862,35 +862,35 @@
       </c>
       <c r="C16" s="2" t="n"/>
       <c r="D16" s="2" t="n">
-        <v>2371000</v>
+        <v>11110000</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Mehnat Poligraf MChJ</t>
+          <t>Ziyo Yog'och MChJ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>224230666</t>
+          <t>312245313</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>20208000074661545001</t>
+          <t>20208000098017876001</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №26/26, НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartn. №10/26, QQS 12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>268021000</v>
+        <v>221196000</v>
       </c>
     </row>
     <row r="17">
@@ -900,37 +900,37 @@
       <c r="B17" t="n">
         <v>109</v>
       </c>
-      <c r="C17" s="2" t="n">
-        <v>8525000</v>
-      </c>
-      <c r="D17" s="2" t="n"/>
+      <c r="C17" s="2" t="n"/>
+      <c r="D17" s="2" t="n">
+        <v>8668000</v>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Qarshi Mehmonxona MChJ</t>
+          <t>Xiva Polimer AJ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>250023319</t>
+          <t>257873684</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20208000275405590001</t>
+          <t>20208000626499181001</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №7756</t>
+          <t>Tovar uchun to'lov, hisob-faktura №1117 06.07.2026,QQS bilan</t>
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>259496000</v>
+        <v>229864000</v>
       </c>
     </row>
     <row r="18">
@@ -940,37 +940,37 @@
       <c r="B18" t="n">
         <v>110</v>
       </c>
-      <c r="C18" s="2" t="n">
-        <v>9596000</v>
-      </c>
-      <c r="D18" s="2" t="n"/>
+      <c r="C18" s="2" t="n"/>
+      <c r="D18" s="2" t="n">
+        <v>5956000</v>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Durdona Dori-Darmon MChJ</t>
+          <t>Lazzat Savdo MChJ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>306318030</t>
+          <t>223066690</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>20208000554383246001</t>
+          <t>20208000466154582001</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №58/26</t>
+          <t>Tovar uchun to'lov, hisob-faktura №6141 06.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>249900000</v>
+        <v>235820000</v>
       </c>
     </row>
     <row r="19">
@@ -980,18 +980,23 @@
       <c r="B19" t="n">
         <v>111</v>
       </c>
-      <c r="C19" s="2" t="n">
-        <v>39557000</v>
-      </c>
-      <c r="D19" s="2" t="n"/>
+      <c r="C19" s="2" t="n"/>
+      <c r="D19" s="2" t="n">
+        <v>2322000</v>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Yangi Asr Bank</t>
+          <t>Sarbon Agro AJ</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>230167378</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000670005672001</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1001,77 +1006,77 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Заработная плата за июнь 2026 г. (перечисление на пластиковые карты)</t>
+          <t>Shartnoma №277/26 bo'yica oldindan to'lov</t>
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>210343000</v>
+        <v>238142000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>46210</v>
+        <v>46209</v>
       </c>
       <c r="B20" t="n">
         <v>112</v>
       </c>
-      <c r="C20" s="2" t="n">
-        <v>3429000</v>
-      </c>
-      <c r="D20" s="2" t="n"/>
+      <c r="C20" s="2" t="n"/>
+      <c r="D20" s="2" t="n">
+        <v>1804000</v>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Oqtosh Qurilish Materiallari MChJ</t>
+          <t>Lazzat Savdo MChJ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>256243523</t>
+          <t>223066690</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>20208000588298767001</t>
+          <t>20208000466154582001</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Аренда помещения за июль, дог. №62/23</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №3969</t>
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>206914000</v>
+        <v>239946000</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>46210</v>
+        <v>46209</v>
       </c>
       <c r="B21" t="n">
         <v>113</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>178341000</v>
+        <v>3808000</v>
       </c>
       <c r="D21" s="2" t="n"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Namangan Sut Mahsulotlari MChJ</t>
+          <t>Qarshi Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>231235630</t>
+          <t>242558726</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20208000785568112001</t>
+          <t>20208000685861603001</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1081,37 +1086,32 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №129/26, QQS bilan</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №214/26, QQS bilan</t>
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>28573000</v>
+        <v>236138000</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>46211</v>
+        <v>46209</v>
       </c>
       <c r="B22" t="n">
         <v>114</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>39525000</v>
+        <v>39557000</v>
       </c>
       <c r="D22" s="2" t="n"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Shahrisabz Avto Ehtiyot AJ</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>362972200</t>
+          <t>Yangi Asr Bank</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>20208000902223626001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1121,197 +1121,197 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №76/26</t>
+          <t>Iyun oyi uchun ish haqi, reestr №2508</t>
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>-10952000</v>
+        <v>196581000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>46212</v>
+        <v>46211</v>
       </c>
       <c r="B23" t="n">
         <v>115</v>
       </c>
-      <c r="C23" s="2" t="n">
-        <v>4350000</v>
-      </c>
-      <c r="D23" s="2" t="n"/>
+      <c r="C23" s="2" t="n"/>
+      <c r="D23" s="2" t="n">
+        <v>6101000</v>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Durdona Dori-Darmon MChJ</t>
+          <t>Xiva Polimer AJ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>306318030</t>
+          <t>257873684</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>20208000554383246001</t>
+          <t>20208000626499181001</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №6041</t>
+          <t>Tovar uchun to'lov, hisob-faktura №9276 08.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>-15302000</v>
+        <v>202682000</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>46213</v>
+        <v>46211</v>
       </c>
       <c r="B24" t="n">
         <v>116</v>
       </c>
-      <c r="C24" s="2" t="n"/>
-      <c r="D24" s="2" t="n">
-        <v>8663000</v>
-      </c>
+      <c r="C24" s="2" t="n">
+        <v>2362000</v>
+      </c>
+      <c r="D24" s="2" t="n"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Andijon Trans Servis XK</t>
+          <t>Namangan Logistik MChJ</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>265178635</t>
+          <t>202331952</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>20208000883316664001</t>
+          <t>20208000540559068001</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №273/26, QQS 12%</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №138/26</t>
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>-6639000</v>
+        <v>200320000</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>46216</v>
+        <v>46212</v>
       </c>
       <c r="B25" t="n">
         <v>117</v>
       </c>
       <c r="C25" s="2" t="n"/>
       <c r="D25" s="2" t="n">
-        <v>21337000</v>
+        <v>41264000</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ziyo Trans Servis MChJ</t>
+          <t>Xiva Polimer AJ</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>233907032</t>
+          <t>257873684</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>20208000722324201001</t>
+          <t>20208000626499181001</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №5280</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №6088</t>
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>14698000</v>
+        <v>241584000</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>46216</v>
+        <v>46212</v>
       </c>
       <c r="B26" t="n">
         <v>118</v>
       </c>
       <c r="C26" s="2" t="n"/>
       <c r="D26" s="2" t="n">
-        <v>7733000</v>
+        <v>4669000</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Jizzax Non AJ</t>
+          <t>Xiva Polimer AJ</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>384578736</t>
+          <t>257873684</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>20208000406264991001</t>
+          <t>20208000626499181001</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Shartnoma №286/26 bo'yicha oldindan to'lov</t>
+          <t>Tovar uchun to'lov, hisob-faktura №1471 09.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>22431000</v>
+        <v>246253000</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>46216</v>
+        <v>46212</v>
       </c>
       <c r="B27" t="n">
         <v>119</v>
       </c>
       <c r="C27" s="2" t="n"/>
       <c r="D27" s="2" t="n">
-        <v>4940000</v>
+        <v>2115000</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Jizzax Non AJ</t>
+          <t>Lazzat Savdo MChJ</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>384578736</t>
+          <t>223066690</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>20208000406264991001</t>
+          <t>20208000466154582001</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1321,157 +1321,157 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №48/26, QQS 12%</t>
+          <t>Shartnoma №56/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>27371000</v>
+        <v>248368000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>46216</v>
+        <v>46212</v>
       </c>
       <c r="B28" t="n">
         <v>120</v>
       </c>
-      <c r="C28" s="2" t="n"/>
-      <c r="D28" s="2" t="n">
-        <v>3803000</v>
-      </c>
+      <c r="C28" s="2" t="n">
+        <v>3429000</v>
+      </c>
+      <c r="D28" s="2" t="n"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Jizzax Non AJ</t>
+          <t>Saodat Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>384578736</t>
+          <t>384857731</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>20208000406264991001</t>
+          <t>20208000469248688001</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №158/26, QQS 12%</t>
+          <t>Bino ijarasi uchun to'lov iyul</t>
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>31174000</v>
+        <v>244939000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>46216</v>
+        <v>46213</v>
       </c>
       <c r="B29" t="n">
         <v>121</v>
       </c>
-      <c r="C29" s="2" t="n">
-        <v>3313000</v>
-      </c>
-      <c r="D29" s="2" t="n"/>
+      <c r="C29" s="2" t="n"/>
+      <c r="D29" s="2" t="n">
+        <v>7404000</v>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Shahrisabz Avto Ehtiyot AJ</t>
+          <t>Xiva Polimer AJ</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>362972200</t>
+          <t>257873684</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>20208000902223626001</t>
+          <t>20208000626499181001</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные матриалы, с/ф №7994</t>
+          <t>Shartnoma №225/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>27861000</v>
+        <v>252343000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>46217</v>
+        <v>46216</v>
       </c>
       <c r="B30" t="n">
         <v>122</v>
       </c>
       <c r="C30" s="2" t="n"/>
       <c r="D30" s="2" t="n">
-        <v>19270000</v>
+        <v>12690000</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Andijon Trans Servis XK</t>
+          <t>Lazzat Savdo MChJ</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>265178635</t>
+          <t>223066690</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>20208000883316664001</t>
+          <t>20208000466154582001</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №8434 14.07.2026, QQS bilan</t>
+          <t>Оплата за товар по с/ф №5458 от 13.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>47131000</v>
+        <v>265033000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>46217</v>
+        <v>46216</v>
       </c>
       <c r="B31" t="n">
         <v>123</v>
       </c>
       <c r="C31" s="2" t="n"/>
       <c r="D31" s="2" t="n">
-        <v>6454000</v>
+        <v>5201000</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Jizzax Non AJ</t>
+          <t>Sarbon Agro AJ</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>384578736</t>
+          <t>230167378</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>20208000406264991001</t>
+          <t>20208000670005672001</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1481,792 +1481,797 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №289/26 от 14.07.2026</t>
+          <t>Предоплата за товар по договору №54/26 от 13.07.2026</t>
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>53585000</v>
+        <v>270234000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>46217</v>
+        <v>46216</v>
       </c>
       <c r="B32" t="n">
         <v>124</v>
       </c>
-      <c r="C32" s="2" t="n">
-        <v>27418000</v>
-      </c>
-      <c r="D32" s="2" t="n"/>
+      <c r="C32" s="2" t="n"/>
+      <c r="D32" s="2" t="n">
+        <v>3452000</v>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Durdona Dori-Darmon MChJ</t>
+          <t>Termiz Logistik MChJ</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>306318030</t>
+          <t>317863528</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>20208000554383246001</t>
+          <t>20208000331666401001</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №342</t>
+          <t>Shartnoma №15/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>26167000</v>
+        <v>273686000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>46218</v>
+        <v>46216</v>
       </c>
       <c r="B33" t="n">
         <v>125</v>
       </c>
-      <c r="C33" s="2" t="n">
-        <v>5394000</v>
-      </c>
-      <c r="D33" s="2" t="n"/>
+      <c r="C33" s="2" t="n"/>
+      <c r="D33" s="2" t="n">
+        <v>3226000</v>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Xiva Polimer AJ</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>257873684</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000626499181001</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>IYUN OYI UCHUN IJTIMOIY SOLIQ</t>
+          <t>Предоплата за товар по дог. №49/26 от 13.07.2026</t>
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>20773000</v>
+        <v>276912000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
-        <v>46218</v>
+        <v>46216</v>
       </c>
       <c r="B34" t="n">
         <v>126</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>5394000</v>
+        <v>3327000</v>
       </c>
       <c r="D34" s="2" t="n"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Andijon Logistik MChJ</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>290703257</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000232420108001</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>НДФЛ за июнь 2026</t>
+          <t>TRANSPORT XIZMATLARI UCHUN TO'LOV, SHARTNOMA №117/26</t>
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>15379000</v>
+        <v>273585000</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>46218</v>
+        <v>46216</v>
       </c>
       <c r="B35" t="n">
         <v>127</v>
       </c>
       <c r="C35" s="2" t="n">
-        <v>28409000</v>
+        <v>3935000</v>
       </c>
       <c r="D35" s="2" t="n"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Omad Moy AJ</t>
+          <t>Nurafshon Logistik XK</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>319688973</t>
+          <t>267357497</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>20208000890097668001</t>
+          <t>20208000958282772001</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartn. №14/26</t>
+          <t>Tovarlar uchun to'lov h/f №97</t>
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>-13030000</v>
+        <v>269650000</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
-        <v>46223</v>
+        <v>46216</v>
       </c>
       <c r="B36" t="n">
         <v>128</v>
       </c>
-      <c r="C36" s="2" t="n"/>
-      <c r="D36" s="2" t="n">
-        <v>7415000</v>
-      </c>
+      <c r="C36" s="2" t="n">
+        <v>14631000</v>
+      </c>
+      <c r="D36" s="2" t="n"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Jizzax Non AJ</t>
+          <t>Qarshi Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>384578736</t>
+          <t>242558726</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>20208000406264991001</t>
+          <t>20208000685861603001</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №165/26, QQS 12%</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №226/26, QQS bilan</t>
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>-5615000</v>
+        <v>255019000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>46223</v>
+        <v>46217</v>
       </c>
       <c r="B37" t="n">
         <v>129</v>
       </c>
-      <c r="C37" s="2" t="n">
-        <v>2805000</v>
-      </c>
-      <c r="D37" s="2" t="n"/>
+      <c r="C37" s="2" t="n"/>
+      <c r="D37" s="2" t="n">
+        <v>3551000</v>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Durdona Dori-Darmon MChJ</t>
+          <t>Xiva Polimer AJ</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>306318030</t>
+          <t>257873684</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>20208000554383246001</t>
+          <t>20208000626499181001</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТОВАРЫ СОГЛАСНО СЧЕТ-ФАКТУРЕ №1779</t>
+          <t>Shartnoma №106/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>-8420000</v>
+        <v>258570000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
-        <v>46224</v>
+        <v>46217</v>
       </c>
       <c r="B38" t="n">
         <v>130</v>
       </c>
       <c r="C38" s="2" t="n"/>
       <c r="D38" s="2" t="n">
-        <v>17032000</v>
+        <v>1766000</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Mehnat Poligraf MChJ</t>
+          <t>Qo'qon Agro Servis MChJ</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>224230666</t>
+          <t>378281519</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>20208000074661545001</t>
+          <t>20208000731544252001</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №4339</t>
+          <t>Mahsulot uchun to'lov, shartnoma №7/26, QQS 12%</t>
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>8612000</v>
+        <v>260336000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>46224</v>
+        <v>46217</v>
       </c>
       <c r="B39" t="n">
         <v>131</v>
       </c>
-      <c r="C39" s="2" t="n"/>
-      <c r="D39" s="2" t="n">
-        <v>7555000</v>
-      </c>
+      <c r="C39" s="2" t="n">
+        <v>6064000</v>
+      </c>
+      <c r="D39" s="2" t="n"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Mehnat Poligraf MChJ</t>
+          <t>Qarshi Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>224230666</t>
+          <t>242558726</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>20208000074661545001</t>
+          <t>20208000685861603001</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №93/26, QQS 12%</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №53/26, QQS bilan</t>
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>16167000</v>
+        <v>254272000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
-        <v>46224</v>
+        <v>46218</v>
       </c>
       <c r="B40" t="n">
         <v>132</v>
       </c>
-      <c r="C40" s="2" t="n">
-        <v>5744000</v>
-      </c>
-      <c r="D40" s="2" t="n"/>
+      <c r="C40" s="2" t="n"/>
+      <c r="D40" s="2" t="n">
+        <v>5354000</v>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Ziyo Yog'och MChJ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>312245313</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000098017876001</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Qo'shilgan qiymat solig'i iyun oyi</t>
+          <t>Shartnoma №247/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>10423000</v>
+        <v>259626000</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>46225</v>
+        <v>46218</v>
       </c>
       <c r="B41" t="n">
         <v>133</v>
       </c>
       <c r="C41" s="2" t="n"/>
       <c r="D41" s="2" t="n">
-        <v>26532000</v>
+        <v>2625000</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Jizzax Non AJ</t>
+          <t>Xiva Polimer AJ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>384578736</t>
+          <t>257873684</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>20208000406264991001</t>
+          <t>20208000626499181001</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №285/26, QQS 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №5383</t>
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>36955000</v>
+        <v>262251000</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
-        <v>46227</v>
+        <v>46219</v>
       </c>
       <c r="B42" t="n">
         <v>134</v>
       </c>
       <c r="C42" s="2" t="n"/>
       <c r="D42" s="2" t="n">
-        <v>49524000</v>
+        <v>9058000</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Mehnat Poligraf MChJ</t>
+          <t>Xiva Polimer AJ</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>224230666</t>
+          <t>257873684</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>20208000074661545001</t>
+          <t>20208000626499181001</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №4243 24.07.2026, QQS bilan</t>
+          <t>Предоплата за товар по договору №6/26 от 16.07.2026</t>
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>86479000</v>
+        <v>271309000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
-        <v>46227</v>
+        <v>46219</v>
       </c>
       <c r="B43" t="n">
         <v>135</v>
       </c>
       <c r="C43" s="2" t="n"/>
       <c r="D43" s="2" t="n">
-        <v>12157000</v>
+        <v>9003000</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Jizzax Non AJ</t>
+          <t>Xiva Polimer AJ</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>384578736</t>
+          <t>257873684</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>20208000406264991001</t>
+          <t>20208000626499181001</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №272/26, QQS 12%</t>
+          <t>Mahsulot uchun to'lov, shartnoma №109/26, QQS 12%</t>
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>98636000</v>
+        <v>280312000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
-        <v>46227</v>
+        <v>46219</v>
       </c>
       <c r="B44" t="n">
         <v>136</v>
       </c>
       <c r="C44" s="2" t="n">
-        <v>2143000</v>
+        <v>5394000</v>
       </c>
       <c r="D44" s="2" t="n"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>20208000474560325001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Elektr energiyasi uchun to'lov iyul</t>
+          <t>Ijtimoiy soliq iyun 2026</t>
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>96493000</v>
+        <v>274918000</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
-        <v>46227</v>
+        <v>46219</v>
       </c>
       <c r="B45" t="n">
         <v>137</v>
       </c>
       <c r="C45" s="2" t="n">
-        <v>2613000</v>
+        <v>5394000</v>
       </c>
       <c r="D45" s="2" t="n"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Omad Moy AJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>319688973</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>20208000890097668001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №8433</t>
+          <t>Jismoniy shaxslar daromad solig'i iyun 2026</t>
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>93880000</v>
+        <v>269524000</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
-        <v>46228</v>
+        <v>46220</v>
       </c>
       <c r="B46" t="n">
         <v>138</v>
       </c>
-      <c r="C46" s="2" t="n">
-        <v>45100000</v>
-      </c>
-      <c r="D46" s="2" t="n"/>
+      <c r="C46" s="2" t="n"/>
+      <c r="D46" s="2" t="n">
+        <v>137954000</v>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-5488)</t>
+          <t>Xiva Polimer AJ</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>257873684</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>16307000345325813417</t>
+          <t>20208000626499181001</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-5488 bo'yicha navbatdagi to'lov (07.2026)</t>
+          <t>Mahsulot uchun to'lov, shartnoma №244/26, QQS 12%</t>
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>48780000</v>
+        <v>407478000</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
-        <v>46230</v>
+        <v>46220</v>
       </c>
       <c r="B47" t="n">
         <v>139</v>
       </c>
       <c r="C47" s="2" t="n"/>
       <c r="D47" s="2" t="n">
-        <v>22135000</v>
+        <v>2833000</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Jizzax Non AJ</t>
+          <t>Xiva Polimer AJ</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>384578736</t>
+          <t>257873684</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>20208000406264991001</t>
+          <t>20208000626499181001</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №187/26, QQS 12%</t>
+          <t>Оплата по счет-фактуре №9707 за поставленный товар</t>
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>70915000</v>
+        <v>410311000</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
-        <v>46230</v>
+        <v>46223</v>
       </c>
       <c r="B48" t="n">
         <v>140</v>
       </c>
       <c r="C48" s="2" t="n"/>
       <c r="D48" s="2" t="n">
-        <v>19104000</v>
+        <v>27948000</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Jizzax Non AJ</t>
+          <t>Xiva Polimer AJ</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>384578736</t>
+          <t>257873684</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>20208000406264991001</t>
+          <t>20208000626499181001</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №2414 от 27.07.2026, в т.ч. НДС 12%</t>
+          <t>Shartnoma №59/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>90019000</v>
+        <v>438259000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
-        <v>46230</v>
+        <v>46223</v>
       </c>
       <c r="B49" t="n">
         <v>141</v>
       </c>
       <c r="C49" s="2" t="n"/>
       <c r="D49" s="2" t="n">
-        <v>15503000</v>
+        <v>5761000</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Jizzax Non AJ</t>
+          <t>Xiva Polimer AJ</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>384578736</t>
+          <t>257873684</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>20208000406264991001</t>
+          <t>20208000626499181001</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>SHARTNOMA №148/26 BO'YICHA OLDINDAN TO'LOV</t>
+          <t>Оплата за продукцию по договору №88/26, НДС 12%</t>
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>105522000</v>
+        <v>444020000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="n">
-        <v>46230</v>
+        <v>46223</v>
       </c>
       <c r="B50" t="n">
         <v>142</v>
       </c>
       <c r="C50" s="2" t="n"/>
       <c r="D50" s="2" t="n">
-        <v>7994000</v>
+        <v>5036000</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Bahor Agro MChJ</t>
+          <t>Xiva Polimer AJ</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>393301673</t>
+          <t>257873684</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>20208000866700056001</t>
+          <t>20208000626499181001</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №8884 27.07.2026, QQS bilan</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №1050</t>
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>113516000</v>
+        <v>449056000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="n">
-        <v>46230</v>
+        <v>46223</v>
       </c>
       <c r="B51" t="n">
         <v>143</v>
       </c>
       <c r="C51" s="2" t="n"/>
       <c r="D51" s="2" t="n">
-        <v>4329000</v>
+        <v>1756000</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Jizzax Non AJ</t>
+          <t>Zarafshon Un Mahsulotlari AJ</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>384578736</t>
+          <t>371763093</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>20208000406264991001</t>
+          <t>20208000181264224001</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2276,867 +2281,867 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Shartnoma №86/26 bo'yicha oldindan to'lov</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №2325</t>
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>117845000</v>
+        <v>450812000</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="n">
-        <v>46230</v>
+        <v>46223</v>
       </c>
       <c r="B52" t="n">
         <v>144</v>
       </c>
-      <c r="C52" s="2" t="n"/>
-      <c r="D52" s="2" t="n">
-        <v>3185000</v>
-      </c>
+      <c r="C52" s="2" t="n">
+        <v>8964000</v>
+      </c>
+      <c r="D52" s="2" t="n"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Jizzax Non AJ</t>
+          <t>Nurafshon Moy MChJ</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>384578736</t>
+          <t>331803035</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>20208000406264991001</t>
+          <t>20208000438324655001</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №169/26, QQS 12%</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №96/26</t>
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>121030000</v>
+        <v>441848000</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="n">
-        <v>46230</v>
+        <v>46224</v>
       </c>
       <c r="B53" t="n">
         <v>145</v>
       </c>
       <c r="C53" s="2" t="n"/>
       <c r="D53" s="2" t="n">
-        <v>2839000</v>
+        <v>5417000</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Jizzax Non AJ</t>
+          <t>Xiva Polimer AJ</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>384578736</t>
+          <t>257873684</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>20208000406264991001</t>
+          <t>20208000626499181001</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №8324 27.07.2026, QQS bilan</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №7381</t>
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>123869000</v>
+        <v>447265000</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
-        <v>46230</v>
+        <v>46224</v>
       </c>
       <c r="B54" t="n">
         <v>146</v>
       </c>
       <c r="C54" s="2" t="n">
-        <v>3590000</v>
+        <v>5647000</v>
       </c>
       <c r="D54" s="2" t="n"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Nihol Meva-Sabzavot MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>264566227</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>20208000988889837001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №102/26</t>
+          <t>QQS iyun 2026 uchun</t>
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>120279000</v>
+        <v>441618000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="n">
-        <v>46230</v>
+        <v>46225</v>
       </c>
       <c r="B55" t="n">
         <v>147</v>
       </c>
-      <c r="C55" s="2" t="n">
-        <v>9183000</v>
-      </c>
-      <c r="D55" s="2" t="n"/>
+      <c r="C55" s="2" t="n"/>
+      <c r="D55" s="2" t="n">
+        <v>16492000</v>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Omad Moy AJ</t>
+          <t>Xiva Polimer AJ</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>319688973</t>
+          <t>257873684</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>20208000890097668001</t>
+          <t>20208000626499181001</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №19/26</t>
+          <t>MAHSULOT UCHUN TO'LOV, SHARTNOMA №263/26, QQS 12%</t>
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>111096000</v>
+        <v>458110000</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="n">
-        <v>46230</v>
+        <v>46225</v>
       </c>
       <c r="B56" t="n">
         <v>148</v>
       </c>
       <c r="C56" s="2" t="n">
-        <v>13180000</v>
+        <v>6866000</v>
       </c>
       <c r="D56" s="2" t="n"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Durdona Dori-Darmon MChJ</t>
+          <t>Andijon Logistik MChJ</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>306318030</t>
+          <t>290703257</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>20208000554383246001</t>
+          <t>20208000232420108001</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №253/26</t>
+          <t>Оплата затранспортные услуги по дог. №239/26</t>
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>97916000</v>
+        <v>451244000</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="n">
-        <v>46231</v>
+        <v>46225</v>
       </c>
       <c r="B57" t="n">
         <v>149</v>
       </c>
-      <c r="C57" s="2" t="n"/>
-      <c r="D57" s="2" t="n">
-        <v>7784000</v>
-      </c>
+      <c r="C57" s="2" t="n">
+        <v>174110000</v>
+      </c>
+      <c r="D57" s="2" t="n"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Mehnat Poligraf MChJ</t>
+          <t>Andijon Logistik MChJ</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>224230666</t>
+          <t>290703257</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>20208000074661545001</t>
+          <t>20208000232420108001</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №7155 за поставленный товар</t>
+          <t>Tovarlar uchun to'lov h/f №9952</t>
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>105700000</v>
+        <v>277134000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="n">
-        <v>46231</v>
+        <v>46226</v>
       </c>
       <c r="B58" t="n">
         <v>150</v>
       </c>
-      <c r="C58" s="2" t="n"/>
-      <c r="D58" s="2" t="n">
-        <v>4745000</v>
-      </c>
+      <c r="C58" s="2" t="n">
+        <v>2663000</v>
+      </c>
+      <c r="D58" s="2" t="n"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Mehnat Tekstil MChJ</t>
+          <t>Andijon Logistik MChJ</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>398717630</t>
+          <t>290703257</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>20208000371812642001</t>
+          <t>20208000232420108001</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №7891</t>
+          <t>Оплата за упаковочные материалы, с/ф №2744</t>
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>110445000</v>
+        <v>274471000</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="n">
-        <v>46231</v>
+        <v>46226</v>
       </c>
       <c r="B59" t="n">
         <v>151</v>
       </c>
-      <c r="C59" s="2" t="n"/>
-      <c r="D59" s="2" t="n">
-        <v>4310000</v>
-      </c>
+      <c r="C59" s="2" t="n">
+        <v>5125000</v>
+      </c>
+      <c r="D59" s="2" t="n"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Jizzax Non AJ</t>
+          <t>Andijon Logistik MChJ</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>384578736</t>
+          <t>290703257</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>20208000406264991001</t>
+          <t>20208000232420108001</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №206/26, QQS 12%</t>
+          <t>Xom ashyo uchun to'lov, shartn. №209/26, QQS bilan</t>
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>114755000</v>
+        <v>269346000</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="n">
-        <v>46232</v>
+        <v>46227</v>
       </c>
       <c r="B60" t="n">
         <v>152</v>
       </c>
       <c r="C60" s="2" t="n"/>
       <c r="D60" s="2" t="n">
-        <v>4684000</v>
+        <v>5525000</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Jizzax Non AJ</t>
+          <t>Xiva Polimer AJ</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>384578736</t>
+          <t>257873684</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>20208000406264991001</t>
+          <t>20208000626499181001</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №3142 29.07.2026, QQS bilan</t>
+          <t>Shartnoma №173/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>119439000</v>
+        <v>274871000</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="n">
-        <v>46233</v>
+        <v>46228</v>
       </c>
       <c r="B61" t="n">
         <v>153</v>
       </c>
       <c r="C61" s="2" t="n">
-        <v>7077000</v>
+        <v>45100000</v>
       </c>
       <c r="D61" s="2" t="n"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Zafar Trans Servis XK</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>350425587</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-5488)</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>20208000646858616001</t>
+          <t>16307000345325813417</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartn. №117/26</t>
+          <t>Kredit shartnomasi L-2025-5488 bo'yicha navbatdagi to'lov (07.2026)</t>
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>112362000</v>
+        <v>229771000</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="n">
-        <v>46234</v>
+        <v>46230</v>
       </c>
       <c r="B62" t="n">
         <v>154</v>
       </c>
       <c r="C62" s="2" t="n"/>
       <c r="D62" s="2" t="n">
-        <v>118997000</v>
+        <v>5276000</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Jizzax Non AJ</t>
+          <t>Xiva Polimer AJ</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>384578736</t>
+          <t>257873684</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>20208000406264991001</t>
+          <t>20208000626499181001</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №1758</t>
+          <t>Tovar uchun to'lov, hisob-faktura №8039 27.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>231359000</v>
+        <v>235047000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="n">
-        <v>46234</v>
+        <v>46230</v>
       </c>
       <c r="B63" t="n">
         <v>155</v>
       </c>
       <c r="C63" s="2" t="n"/>
       <c r="D63" s="2" t="n">
-        <v>2357000</v>
+        <v>3721000</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Bog'ishamol Oziq-ovqat Savdo AJ</t>
+          <t>Sarbon Agro AJ</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>228782815</t>
+          <t>230167378</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>20208000977315442001</t>
+          <t>20208000670005672001</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №5007 31.07.2026, QQS bilan</t>
+          <t>Mahsulot uchun to'lov, shartnoma №83/26, QQS 12%</t>
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>233716000</v>
+        <v>238768000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="n">
-        <v>46234</v>
+        <v>46230</v>
       </c>
       <c r="B64" t="n">
         <v>156</v>
       </c>
-      <c r="C64" s="2" t="n"/>
-      <c r="D64" s="2" t="n">
-        <v>2323000</v>
-      </c>
+      <c r="C64" s="2" t="n">
+        <v>2143000</v>
+      </c>
+      <c r="D64" s="2" t="n"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Mehnat Poligraf MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>224230666</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>20208000074661545001</t>
+          <t>20208000585196889001</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №3953</t>
+          <t>Elektr energiyasi uchun to'lov iyul</t>
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>236039000</v>
+        <v>236625000</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="n">
-        <v>46234</v>
+        <v>46230</v>
       </c>
       <c r="B65" t="n">
         <v>157</v>
       </c>
       <c r="C65" s="2" t="n">
-        <v>300000</v>
+        <v>5676000</v>
       </c>
       <c r="D65" s="2" t="n"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Yangi Asr Bank</t>
+          <t>Andijon Logistik MChJ</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>290703257</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000232420108001</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Hisob-kassa xizmati uchun haq</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №77/26</t>
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>235739000</v>
+        <v>230949000</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="n">
-        <v>46237</v>
+        <v>46230</v>
       </c>
       <c r="B66" t="n">
         <v>158</v>
       </c>
-      <c r="C66" s="2" t="n"/>
-      <c r="D66" s="2" t="n">
-        <v>21575000</v>
-      </c>
+      <c r="C66" s="2" t="n">
+        <v>14160000</v>
+      </c>
+      <c r="D66" s="2" t="n"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Jizzax Non AJ</t>
+          <t>Qo'qon Sut Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>384578736</t>
+          <t>297220069</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>20208000406264991001</t>
+          <t>20208000222362626001</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №74/26, QQS 12%</t>
+          <t>Xom ashyo uchun to'lov, shartn. №195/26, QQS bilan</t>
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>257314000</v>
+        <v>216789000</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="n">
-        <v>46237</v>
+        <v>46230</v>
       </c>
       <c r="B67" t="n">
         <v>159</v>
       </c>
-      <c r="C67" s="2" t="n"/>
-      <c r="D67" s="2" t="n">
-        <v>12902000</v>
-      </c>
+      <c r="C67" s="2" t="n">
+        <v>27736000</v>
+      </c>
+      <c r="D67" s="2" t="n"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Jizzax Non AJ</t>
+          <t>Andijon Logistik MChJ</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>384578736</t>
+          <t>290703257</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>20208000406264991001</t>
+          <t>20208000232420108001</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lovh/f №1413</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №217/26, QQS bilan</t>
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>270216000</v>
+        <v>189053000</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="n">
-        <v>46237</v>
+        <v>46231</v>
       </c>
       <c r="B68" t="n">
         <v>160</v>
       </c>
-      <c r="C68" s="2" t="n">
-        <v>66177000</v>
-      </c>
-      <c r="D68" s="2" t="n"/>
+      <c r="C68" s="2" t="n"/>
+      <c r="D68" s="2" t="n">
+        <v>3088000</v>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Kamalak Farm Savdo MChJ</t>
+          <t>Sarbon Agro AJ</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>297349587</t>
+          <t>230167378</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>20208000889492055001</t>
+          <t>20208000670005672001</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №7024</t>
+          <t>Mahsulot uchun to'lov, shartnoma №104/26, QQS 12%</t>
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>204039000</v>
+        <v>192141000</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="n">
-        <v>46238</v>
+        <v>46233</v>
       </c>
       <c r="B69" t="n">
         <v>161</v>
       </c>
       <c r="C69" s="2" t="n"/>
       <c r="D69" s="2" t="n">
-        <v>9852000</v>
+        <v>36899000</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Olmaliq Yog'och MChJ</t>
+          <t>Xiva Polimer AJ</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>271673574</t>
+          <t>257873684</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>20208000779582827001</t>
+          <t>20208000626499181001</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>MAHSULOT UCHUN TO'LOV, SHARTNOMA №154/26, QQS 12%</t>
+          <t>TOVAR UCHUN TO'LOV, HISOB-FAKTURA №8256 30.07.2026, QQS BILAN</t>
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>213891000</v>
+        <v>229040000</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="n">
-        <v>46238</v>
+        <v>46233</v>
       </c>
       <c r="B70" t="n">
         <v>162</v>
       </c>
       <c r="C70" s="2" t="n"/>
       <c r="D70" s="2" t="n">
-        <v>8423000</v>
+        <v>5799000</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Bahor Agro MChJ</t>
+          <t>Xiva Polimer AJ</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>393301673</t>
+          <t>257873684</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>20208000866700056001</t>
+          <t>20208000626499181001</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №1758 от 04.08.2026, в т.ч. НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartnoma №269/26, QQS 12%</t>
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>222314000</v>
+        <v>234839000</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="n">
-        <v>46238</v>
+        <v>46234</v>
       </c>
       <c r="B71" t="n">
         <v>163</v>
       </c>
       <c r="C71" s="2" t="n">
-        <v>12572000</v>
+        <v>300000</v>
       </c>
       <c r="D71" s="2" t="n"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Zafar Mato AJ</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>258485773</t>
+          <t>Yangi Asr Bank</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>20208000646924868001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartn. №85/26, QQS bilan</t>
+          <t>Комиссия банка за расчетно-кассовое обслуживание за июль</t>
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>209742000</v>
+        <v>234539000</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="n">
-        <v>46238</v>
+        <v>46237</v>
       </c>
       <c r="B72" t="n">
         <v>164</v>
       </c>
       <c r="C72" s="2" t="n">
-        <v>22450000</v>
+        <v>11655000</v>
       </c>
       <c r="D72" s="2" t="n"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Nihol Meva-Sabzavot MChJ</t>
+          <t>Andijon Logistik MChJ</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>264566227</t>
+          <t>290703257</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>20208000988889837001</t>
+          <t>20208000232420108001</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №6091</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №234/26</t>
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>187292000</v>
+        <v>222884000</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="n">
-        <v>46240</v>
+        <v>46237</v>
       </c>
       <c r="B73" t="n">
         <v>165</v>
       </c>
       <c r="C73" s="2" t="n">
-        <v>39724000</v>
+        <v>17242000</v>
       </c>
       <c r="D73" s="2" t="n"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Yangi Asr Bank</t>
+          <t>Nurafshon Logistik XK</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>267357497</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000958282772001</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3146,597 +3151,592 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Iyul oyi uchun ish haqi, reestr №5716</t>
+          <t>Tovarlar uchun to'lov h/f №4656</t>
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>147568000</v>
+        <v>205642000</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="n">
-        <v>46244</v>
+        <v>46238</v>
       </c>
       <c r="B74" t="n">
         <v>166</v>
       </c>
       <c r="C74" s="2" t="n">
-        <v>3443000</v>
+        <v>39724000</v>
       </c>
       <c r="D74" s="2" t="n"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Oqtosh Qurilish Materiallari MChJ</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>256243523</t>
+          <t>Yangi Asr Bank</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>20208000588298767001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Ijara haqi avgust oyi uchun, shartn. №62/23</t>
+          <t>Iyul oyi uchun ish haqi, reestr №9527</t>
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>144125000</v>
+        <v>165918000</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="n">
-        <v>46244</v>
+        <v>46241</v>
       </c>
       <c r="B75" t="n">
         <v>167</v>
       </c>
       <c r="C75" s="2" t="n">
-        <v>9587000</v>
+        <v>7874000</v>
       </c>
       <c r="D75" s="2" t="n"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Nihol Meva-Sabzavot MChJ</t>
+          <t>Nurafshon Logistik XK</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>264566227</t>
+          <t>267357497</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>20208000988889837001</t>
+          <t>20208000958282772001</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №252/26, QQS bilan</t>
+          <t>Оплата за товары согласно счет-фактуре №5244</t>
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>134538000</v>
+        <v>158044000</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="n">
-        <v>46245</v>
+        <v>46244</v>
       </c>
       <c r="B76" t="n">
         <v>168</v>
       </c>
       <c r="C76" s="2" t="n"/>
       <c r="D76" s="2" t="n">
-        <v>40061000</v>
+        <v>63649000</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Jizzax Non AJ</t>
+          <t>Xiva Polimer AJ</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>384578736</t>
+          <t>257873684</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>20208000406264991001</t>
+          <t>20208000626499181001</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Yetkazilgan tvar uchun to'lov h/f №3096</t>
+          <t>Оплата за продукцию по дог. №33/26, НДС 12%</t>
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>174599000</v>
+        <v>221693000</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="n">
-        <v>46245</v>
+        <v>46244</v>
       </c>
       <c r="B77" t="n">
         <v>169</v>
       </c>
       <c r="C77" s="2" t="n"/>
       <c r="D77" s="2" t="n">
-        <v>19813000</v>
+        <v>54105000</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Mehnat Poligraf MChJ</t>
+          <t>Xiva Polimer AJ</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>224230666</t>
+          <t>257873684</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>20208000074661545001</t>
+          <t>20208000626499181001</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №5516 от 11.08.2026, в т.ч. НДС 12%</t>
+          <t>Shartnoma №64/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>194412000</v>
+        <v>275798000</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="n">
-        <v>46246</v>
+        <v>46244</v>
       </c>
       <c r="B78" t="n">
         <v>170</v>
       </c>
       <c r="C78" s="2" t="n"/>
       <c r="D78" s="2" t="n">
-        <v>10741000</v>
+        <v>40827000</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Jizzax Non AJ</t>
+          <t>Xiva Polimer AJ</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>384578736</t>
+          <t>257873684</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>20208000406264991001</t>
+          <t>20208000626499181001</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №229/26, QQS 12%</t>
+          <t>SHARTNOMA №270/26 BO'YICHA OLDINDAN TO'LOV</t>
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>205153000</v>
+        <v>316625000</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="n">
-        <v>46247</v>
+        <v>46244</v>
       </c>
       <c r="B79" t="n">
         <v>171</v>
       </c>
-      <c r="C79" s="2" t="n"/>
-      <c r="D79" s="2" t="n">
-        <v>11291000</v>
-      </c>
+      <c r="C79" s="2" t="n">
+        <v>3443000</v>
+      </c>
+      <c r="D79" s="2" t="n"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Bahor Agro MChJ</t>
+          <t>Saodat Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>393301673</t>
+          <t>384857731</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>20208000866700056001</t>
+          <t>20208000469248688001</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №142/26, НДС 12%</t>
+          <t>Ijara haqi avgust oyi uchun, shartnoma №95/25</t>
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>216444000</v>
+        <v>313182000</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="n">
-        <v>46247</v>
+        <v>46244</v>
       </c>
       <c r="B80" t="n">
         <v>172</v>
       </c>
       <c r="C80" s="2" t="n">
-        <v>33567000</v>
+        <v>6325000</v>
       </c>
       <c r="D80" s="2" t="n"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Nihol Meva-Sabzavot MChJ</t>
+          <t>Qarshi Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>264566227</t>
+          <t>242558726</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>20208000988889837001</t>
+          <t>20208000685861603001</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №174/26</t>
+          <t>Tovarlar uchun to'lov h/f №9092</t>
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>182877000</v>
+        <v>306857000</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="n">
-        <v>46248</v>
+        <v>46244</v>
       </c>
       <c r="B81" t="n">
         <v>173</v>
       </c>
-      <c r="C81" s="2" t="n"/>
-      <c r="D81" s="2" t="n">
-        <v>73178000</v>
-      </c>
+      <c r="C81" s="2" t="n">
+        <v>16985000</v>
+      </c>
+      <c r="D81" s="2" t="n"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Mehnat Poligraf MChJ</t>
+          <t>Andijon Logistik MChJ</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>224230666</t>
+          <t>290703257</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>20208000074661545001</t>
+          <t>20208000232420108001</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №6952 от 14.08.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за транспортные услуги по договору №171/26</t>
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>256055000</v>
+        <v>289872000</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="n">
-        <v>46251</v>
+        <v>46245</v>
       </c>
       <c r="B82" t="n">
         <v>174</v>
       </c>
       <c r="C82" s="2" t="n"/>
       <c r="D82" s="2" t="n">
-        <v>20963000</v>
+        <v>13313000</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Mehnat Tekstil MChJ</t>
+          <t>Xiva Polimer AJ</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>398717630</t>
+          <t>257873684</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>20208000371812642001</t>
+          <t>20208000626499181001</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №172/26, НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartnoma №224/26, QQS 12%</t>
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>277018000</v>
+        <v>303185000</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="n">
-        <v>46251</v>
+        <v>46246</v>
       </c>
       <c r="B83" t="n">
         <v>175</v>
       </c>
-      <c r="C83" s="2" t="n"/>
-      <c r="D83" s="2" t="n">
-        <v>15719000</v>
-      </c>
+      <c r="C83" s="2" t="n">
+        <v>20621000</v>
+      </c>
+      <c r="D83" s="2" t="n"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Jizzax Non AJ</t>
+          <t>Andijon Logistik MChJ</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>384578736</t>
+          <t>290703257</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>20208000406264991001</t>
+          <t>20208000232420108001</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №7716</t>
+          <t>Tovarlar uchun to'lov h/f №8724</t>
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>292737000</v>
+        <v>282564000</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="n">
-        <v>46251</v>
+        <v>46247</v>
       </c>
       <c r="B84" t="n">
         <v>176</v>
       </c>
       <c r="C84" s="2" t="n"/>
       <c r="D84" s="2" t="n">
-        <v>13616000</v>
+        <v>25148000</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Jizzax Non AJ</t>
+          <t>Xiva Polimer AJ</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>384578736</t>
+          <t>257873684</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>20208000406264991001</t>
+          <t>20208000626499181001</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Shartnoma №194/26 bo'yicha oldindan to'lov</t>
+          <t>Mahsulot uchun to'lov, shartnoma №27/26, QQS 12%</t>
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>306353000</v>
+        <v>307712000</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="n">
-        <v>46251</v>
+        <v>46247</v>
       </c>
       <c r="B85" t="n">
         <v>177</v>
       </c>
       <c r="C85" s="2" t="n"/>
       <c r="D85" s="2" t="n">
-        <v>6940000</v>
+        <v>15538000</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Mehnat Poligraf MChJ</t>
+          <t>Xiva Polimer AJ</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>224230666</t>
+          <t>257873684</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>20208000074661545001</t>
+          <t>20208000626499181001</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Shartnoma №118/26 bo'yicha oldindan to'lov</t>
+          <t>Shartnoma №83/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>313293000</v>
+        <v>323250000</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="n">
-        <v>46251</v>
+        <v>46247</v>
       </c>
       <c r="B86" t="n">
         <v>178</v>
       </c>
-      <c r="C86" s="2" t="n">
-        <v>5417000</v>
-      </c>
-      <c r="D86" s="2" t="n"/>
+      <c r="C86" s="2" t="n"/>
+      <c r="D86" s="2" t="n">
+        <v>12638000</v>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Lazzat Savdo MChJ</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>223066690</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000466154582001</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Социальный налог за июль 2026 г.</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №5434</t>
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>307876000</v>
+        <v>335888000</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="n">
-        <v>46251</v>
+        <v>46247</v>
       </c>
       <c r="B87" t="n">
         <v>179</v>
       </c>
       <c r="C87" s="2" t="n">
-        <v>5417000</v>
+        <v>42191000</v>
       </c>
       <c r="D87" s="2" t="n"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Andijon Logistik MChJ</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>290703257</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000232420108001</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>НДФЛ за июл 2026</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №171/26, QQS bilan</t>
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>302459000</v>
+        <v>293697000</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="n">
-        <v>46253</v>
+        <v>46248</v>
       </c>
       <c r="B88" t="n">
         <v>180</v>
       </c>
-      <c r="C88" s="2" t="n">
-        <v>91643000</v>
-      </c>
-      <c r="D88" s="2" t="n"/>
+      <c r="C88" s="2" t="n"/>
+      <c r="D88" s="2" t="n">
+        <v>7704000</v>
+      </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Kamalak Farm Savdo MChJ</t>
+          <t>Termiz Logistik MChJ</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>297349587</t>
+          <t>317863528</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>20208000889492055001</t>
+          <t>20208000331666401001</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -3746,37 +3746,37 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №245/26</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №8698</t>
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>210816000</v>
+        <v>301401000</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="n">
-        <v>46258</v>
+        <v>46248</v>
       </c>
       <c r="B89" t="n">
         <v>181</v>
       </c>
-      <c r="C89" s="2" t="n"/>
-      <c r="D89" s="2" t="n">
-        <v>13396000</v>
-      </c>
+      <c r="C89" s="2" t="n">
+        <v>53147000</v>
+      </c>
+      <c r="D89" s="2" t="n"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Jizzax Non AJ</t>
+          <t>Nurafshon Logistik XK</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>384578736</t>
+          <t>267357497</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>20208000406264991001</t>
+          <t>20208000958282772001</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -3786,37 +3786,37 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>SHARTNOMA №246/26 BO'YICHA OLDINDAN TO'LOV</t>
+          <t>Tovarlar uchun to'lov h/f №9670</t>
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>224212000</v>
+        <v>248254000</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="n">
-        <v>46258</v>
+        <v>46251</v>
       </c>
       <c r="B90" t="n">
         <v>182</v>
       </c>
       <c r="C90" s="2" t="n"/>
       <c r="D90" s="2" t="n">
-        <v>13193000</v>
+        <v>38651000</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Bog'ishamol Oziq-ovqat Savdo AJ</t>
+          <t>Xiva Polimer AJ</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>228782815</t>
+          <t>257873684</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>20208000977315442001</t>
+          <t>20208000626499181001</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -3826,37 +3826,37 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Shartnoma №145/26 bo'yicha oldindan to'lov</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №6598</t>
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>237405000</v>
+        <v>286905000</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="n">
-        <v>46258</v>
+        <v>46251</v>
       </c>
       <c r="B91" t="n">
         <v>183</v>
       </c>
       <c r="C91" s="2" t="n"/>
       <c r="D91" s="2" t="n">
-        <v>12153000</v>
+        <v>6565000</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Jizzax Non AJ</t>
+          <t>Lazzat Savdo MChJ</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>384578736</t>
+          <t>223066690</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>20208000406264991001</t>
+          <t>20208000466154582001</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -3866,392 +3866,397 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №290/26 от 24.08.2026</t>
+          <t>Оплата по счет-фактуре №5550 за поставленный товар</t>
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>249558000</v>
+        <v>293470000</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="n">
-        <v>46258</v>
+        <v>46251</v>
       </c>
       <c r="B92" t="n">
         <v>184</v>
       </c>
-      <c r="C92" s="2" t="n"/>
-      <c r="D92" s="2" t="n">
-        <v>6260000</v>
-      </c>
+      <c r="C92" s="2" t="n">
+        <v>5417000</v>
+      </c>
+      <c r="D92" s="2" t="n"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Jizzax Non AJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>384578736</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>20208000406264991001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Shartnoma №87/26 bo'yicha oldindan to'lov</t>
+          <t>Iyul oyi uchun ijtimoiy soliq</t>
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>255818000</v>
+        <v>288053000</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="n">
-        <v>46258</v>
+        <v>46251</v>
       </c>
       <c r="B93" t="n">
         <v>185</v>
       </c>
       <c r="C93" s="2" t="n">
-        <v>2152000</v>
+        <v>5417000</v>
       </c>
       <c r="D93" s="2" t="n"/>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>20208000474560325001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Elektr energiyasi uchun to'lov avgust</t>
+          <t>НДФЛ за июль 2026</t>
         </is>
       </c>
       <c r="J93" s="2" t="n">
-        <v>253666000</v>
+        <v>282636000</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="n">
-        <v>46258</v>
+        <v>46252</v>
       </c>
       <c r="B94" t="n">
         <v>186</v>
       </c>
-      <c r="C94" s="2" t="n">
-        <v>5816000</v>
-      </c>
-      <c r="D94" s="2" t="n"/>
+      <c r="C94" s="2" t="n"/>
+      <c r="D94" s="2" t="n">
+        <v>9177000</v>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Ziyo Yog'och MChJ</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>312245313</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000098017876001</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>QQS iyul 2026 uchun</t>
+          <t>Оплата за продукцию по дог. №161/26, НДС 12%</t>
         </is>
       </c>
       <c r="J94" s="2" t="n">
-        <v>247850000</v>
+        <v>291813000</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="n">
-        <v>46258</v>
+        <v>46254</v>
       </c>
       <c r="B95" t="n">
         <v>187</v>
       </c>
-      <c r="C95" s="2" t="n">
-        <v>10041000</v>
-      </c>
-      <c r="D95" s="2" t="n"/>
+      <c r="C95" s="2" t="n"/>
+      <c r="D95" s="2" t="n">
+        <v>25507000</v>
+      </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Durdona Dori-Darmon MChJ</t>
+          <t>Lazzat Savdo MChJ</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>306318030</t>
+          <t>223066690</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>20208000554383246001</t>
+          <t>20208000466154582001</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartn. №258/26</t>
+          <t>Tovar uchun to'lov, hisob-faktura №9109 20.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J95" s="2" t="n">
-        <v>237809000</v>
+        <v>317320000</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="n">
-        <v>46258</v>
+        <v>46255</v>
       </c>
       <c r="B96" t="n">
         <v>188</v>
       </c>
-      <c r="C96" s="2" t="n">
-        <v>21319000</v>
-      </c>
-      <c r="D96" s="2" t="n"/>
+      <c r="C96" s="2" t="n"/>
+      <c r="D96" s="2" t="n">
+        <v>52547000</v>
+      </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Qarshi Mehmonxona MChJ</t>
+          <t>Xiva Polimer AJ</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>250023319</t>
+          <t>257873684</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>20208000275405590001</t>
+          <t>20208000626499181001</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №30/26</t>
+          <t>Shartnoma №202/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J96" s="2" t="n">
-        <v>216490000</v>
+        <v>369867000</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="n">
-        <v>46259</v>
+        <v>46255</v>
       </c>
       <c r="B97" t="n">
         <v>189</v>
       </c>
-      <c r="C97" s="2" t="n"/>
-      <c r="D97" s="2" t="n">
-        <v>49889000</v>
-      </c>
+      <c r="C97" s="2" t="n">
+        <v>8672000</v>
+      </c>
+      <c r="D97" s="2" t="n"/>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Mehnat Poligraf MChJ</t>
+          <t>Andijon Logistik MChJ</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>224230666</t>
+          <t>290703257</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>20208000074661545001</t>
+          <t>20208000232420108001</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТОВАР ПО СЧЕТ-ФАКТУРЕ №9568 ОТ 25.08.2026, В Т.Ч. НДС 12%</t>
+          <t>Transport xizmatlari uchun to'lov, shartn. №236/26</t>
         </is>
       </c>
       <c r="J97" s="2" t="n">
-        <v>266379000</v>
+        <v>361195000</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="n">
-        <v>46259</v>
+        <v>46258</v>
       </c>
       <c r="B98" t="n">
         <v>190</v>
       </c>
       <c r="C98" s="2" t="n"/>
       <c r="D98" s="2" t="n">
-        <v>19244000</v>
+        <v>36747000</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Mehnat Tekstil MChJ</t>
+          <t>Lazzat Savdo MChJ</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>398717630</t>
+          <t>223066690</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>20208000371812642001</t>
+          <t>20208000466154582001</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №7827 от 25.08.2026, в т.ч. НДС 12%</t>
+          <t>Tovar uchun to'lov, hisob-faktura №8608 24.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J98" s="2" t="n">
-        <v>285623000</v>
+        <v>397942000</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="n">
-        <v>46259</v>
+        <v>46258</v>
       </c>
       <c r="B99" t="n">
         <v>191</v>
       </c>
-      <c r="C99" s="2" t="n">
-        <v>45100000</v>
-      </c>
-      <c r="D99" s="2" t="n"/>
+      <c r="C99" s="2" t="n"/>
+      <c r="D99" s="2" t="n">
+        <v>6765000</v>
+      </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-5488)</t>
+          <t>Ziyo Yog'och MChJ</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>312245313</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>16307000345325813417</t>
+          <t>20208000098017876001</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-5488 bo'yicha navbatdagi to'lov (08.2026)</t>
+          <t>Shartnoma №98/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J99" s="2" t="n">
-        <v>240523000</v>
+        <v>404707000</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="n">
-        <v>46260</v>
+        <v>46258</v>
       </c>
       <c r="B100" t="n">
         <v>192</v>
       </c>
       <c r="C100" s="2" t="n">
-        <v>32149000</v>
+        <v>5617000</v>
       </c>
       <c r="D100" s="2" t="n"/>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Durdona Dori-Darmon MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>306318030</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>20208000554383246001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №282/26, QQS bilan</t>
+          <t>QQS iyul 2026 uchun</t>
         </is>
       </c>
       <c r="J100" s="2" t="n">
-        <v>208374000</v>
+        <v>399090000</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="n">
-        <v>46261</v>
+        <v>46258</v>
       </c>
       <c r="B101" t="n">
         <v>193</v>
       </c>
-      <c r="C101" s="2" t="n"/>
-      <c r="D101" s="2" t="n">
-        <v>18501000</v>
-      </c>
+      <c r="C101" s="2" t="n">
+        <v>5681000</v>
+      </c>
+      <c r="D101" s="2" t="n"/>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Jizzax Non AJ</t>
+          <t>Namangan Logistik MChJ</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>384578736</t>
+          <t>202331952</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>20208000406264991001</t>
+          <t>20208000540559068001</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -4261,37 +4266,37 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №160/26, QQS 12%</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №172/26</t>
         </is>
       </c>
       <c r="J101" s="2" t="n">
-        <v>226875000</v>
+        <v>393409000</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="n">
-        <v>46261</v>
+        <v>46258</v>
       </c>
       <c r="B102" t="n">
         <v>194</v>
       </c>
-      <c r="C102" s="2" t="n"/>
-      <c r="D102" s="2" t="n">
-        <v>9769000</v>
-      </c>
+      <c r="C102" s="2" t="n">
+        <v>6715000</v>
+      </c>
+      <c r="D102" s="2" t="n"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Jizzax Non AJ</t>
+          <t>Nurafshon Logistik XK</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>384578736</t>
+          <t>267357497</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>20208000406264991001</t>
+          <t>20208000958282772001</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -4301,77 +4306,72 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №614</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №42/26</t>
         </is>
       </c>
       <c r="J102" s="2" t="n">
-        <v>236644000</v>
+        <v>386694000</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="n">
-        <v>46262</v>
+        <v>46258</v>
       </c>
       <c r="B103" t="n">
         <v>195</v>
       </c>
-      <c r="C103" s="2" t="n"/>
-      <c r="D103" s="2" t="n">
-        <v>25787000</v>
-      </c>
+      <c r="C103" s="2" t="n">
+        <v>65907000</v>
+      </c>
+      <c r="D103" s="2" t="n"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Ziyo Trans Servis MChJ</t>
+          <t>Nihol Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>233907032</t>
+          <t>256622789</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>20208000722324201001</t>
+          <t>20208000888983796001</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №8047 28.08.2026, QQS bilan</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №79/26</t>
         </is>
       </c>
       <c r="J103" s="2" t="n">
-        <v>262431000</v>
+        <v>320787000</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="n">
-        <v>46265</v>
+        <v>46259</v>
       </c>
       <c r="B104" t="n">
         <v>196</v>
       </c>
-      <c r="C104" s="2" t="n"/>
-      <c r="D104" s="2" t="n">
-        <v>44839000</v>
-      </c>
+      <c r="C104" s="2" t="n">
+        <v>45100000</v>
+      </c>
+      <c r="D104" s="2" t="n"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Jizzax Non AJ</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>384578736</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-5488)</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>20208000406264991001</t>
+          <t>16307000345325813417</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -4381,72 +4381,77 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №4182 31.08.2026, QQS bilan</t>
+          <t>Kredit shartnomasi L-2025-5488 bo'yicha navbatdagi to'lov (08.2026)</t>
         </is>
       </c>
       <c r="J104" s="2" t="n">
-        <v>307270000</v>
+        <v>275687000</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="n">
-        <v>46265</v>
+        <v>46259</v>
       </c>
       <c r="B105" t="n">
         <v>197</v>
       </c>
-      <c r="C105" s="2" t="n"/>
-      <c r="D105" s="2" t="n">
-        <v>6602000</v>
-      </c>
+      <c r="C105" s="2" t="n">
+        <v>71745000</v>
+      </c>
+      <c r="D105" s="2" t="n"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Mehnat Poligraf MChJ</t>
+          <t>Nurafshon Moy MChJ</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>224230666</t>
+          <t>331803035</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>20208000074661545001</t>
+          <t>20208000438324655001</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Shartnoma №166/26 bo'yicha oldindan to'lov</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №29/26</t>
         </is>
       </c>
       <c r="J105" s="2" t="n">
-        <v>313872000</v>
+        <v>203942000</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="n">
-        <v>46265</v>
+        <v>46260</v>
       </c>
       <c r="B106" t="n">
         <v>198</v>
       </c>
-      <c r="C106" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D106" s="2" t="n"/>
+      <c r="C106" s="2" t="n"/>
+      <c r="D106" s="2" t="n">
+        <v>9073000</v>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Yangi Asr Bank</t>
+          <t>Lazzat Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>223066690</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000466154582001</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -4456,712 +4461,707 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Hisob-kassa xizmati uchun haq</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №2638</t>
         </is>
       </c>
       <c r="J106" s="2" t="n">
-        <v>313572000</v>
+        <v>213015000</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="n">
-        <v>46265</v>
+        <v>46260</v>
       </c>
       <c r="B107" t="n">
         <v>199</v>
       </c>
       <c r="C107" s="2" t="n">
-        <v>9913000</v>
+        <v>2152000</v>
       </c>
       <c r="D107" s="2" t="n"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Qarshi Mehmonxona MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>250023319</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>20208000275405590001</t>
+          <t>20208000585196889001</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №213/26</t>
+          <t>Elektr energiyasi uchun to'lov</t>
         </is>
       </c>
       <c r="J107" s="2" t="n">
-        <v>303659000</v>
+        <v>210863000</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="n">
-        <v>46265</v>
+        <v>46260</v>
       </c>
       <c r="B108" t="n">
         <v>200</v>
       </c>
       <c r="C108" s="2" t="n">
-        <v>60105000</v>
+        <v>9358000</v>
       </c>
       <c r="D108" s="2" t="n"/>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Nihol Meva-Sabzavot MChJ</t>
+          <t>Andijon Logistik MChJ</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>264566227</t>
+          <t>290703257</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>20208000988889837001</t>
+          <t>20208000232420108001</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №28/26, QQS bilan</t>
+          <t>Tovarlar uchun to'lov h/f №2061</t>
         </is>
       </c>
       <c r="J108" s="2" t="n">
-        <v>243554000</v>
+        <v>201505000</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="n">
-        <v>46269</v>
+        <v>46262</v>
       </c>
       <c r="B109" t="n">
         <v>201</v>
       </c>
       <c r="C109" s="2" t="n"/>
       <c r="D109" s="2" t="n">
-        <v>258432000</v>
+        <v>10372000</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Jizzax Non AJ</t>
+          <t>Xiva Polimer AJ</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>384578736</t>
+          <t>257873684</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>20208000406264991001</t>
+          <t>20208000626499181001</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Shartnoma №254/26 bo'yicha oldindan to'lov</t>
+          <t>Mahsulot uchun to'lov, shartnoma №40/26, QQS 12%</t>
         </is>
       </c>
       <c r="J109" s="2" t="n">
-        <v>501986000</v>
+        <v>211877000</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="n">
-        <v>46269</v>
+        <v>46262</v>
       </c>
       <c r="B110" t="n">
         <v>202</v>
       </c>
-      <c r="C110" s="2" t="n"/>
-      <c r="D110" s="2" t="n">
-        <v>15177000</v>
-      </c>
+      <c r="C110" s="2" t="n">
+        <v>12302000</v>
+      </c>
+      <c r="D110" s="2" t="n"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Jizzax Non AJ</t>
+          <t>Andijon Logistik MChJ</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>384578736</t>
+          <t>290703257</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>20208000406264991001</t>
+          <t>20208000232420108001</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №5727 04.09.2026, QQS bilan</t>
+          <t>Mateiallar uchun oldindan to'lov, shartnoma №253/26</t>
         </is>
       </c>
       <c r="J110" s="2" t="n">
-        <v>517163000</v>
+        <v>199575000</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="n">
-        <v>46272</v>
+        <v>46265</v>
       </c>
       <c r="B111" t="n">
         <v>203</v>
       </c>
       <c r="C111" s="2" t="n"/>
       <c r="D111" s="2" t="n">
-        <v>5852000</v>
+        <v>39781000</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Jizzax Non AJ</t>
+          <t>Xiva Polimer AJ</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>384578736</t>
+          <t>257873684</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>20208000406264991001</t>
+          <t>20208000626499181001</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №5372 от 07.09.2026, в т.ч. НДС 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №8050</t>
         </is>
       </c>
       <c r="J111" s="2" t="n">
-        <v>523015000</v>
+        <v>239356000</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="n">
-        <v>46272</v>
+        <v>46265</v>
       </c>
       <c r="B112" t="n">
         <v>204</v>
       </c>
       <c r="C112" s="2" t="n">
-        <v>3187000</v>
+        <v>300000</v>
       </c>
       <c r="D112" s="2" t="n"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Oqtosh Qurilish Materiallari MChJ</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>256243523</t>
+          <t>Yangi Asr Bank</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>20208000588298767001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Bino ijarasi uchun to'lov sentyabr</t>
+          <t>Bank xizmati uchun komissiya</t>
         </is>
       </c>
       <c r="J112" s="2" t="n">
-        <v>519828000</v>
+        <v>239056000</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="n">
-        <v>46272</v>
+        <v>46265</v>
       </c>
       <c r="B113" t="n">
         <v>205</v>
       </c>
       <c r="C113" s="2" t="n">
-        <v>16424000</v>
+        <v>6145000</v>
       </c>
       <c r="D113" s="2" t="n"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Durdona Dori-Darmon MChJ</t>
+          <t>Nihol Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>306318030</t>
+          <t>256622789</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>20208000554383246001</t>
+          <t>20208000888983796001</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №8907</t>
+          <t>Оплата за товары согласно с/ф №9603</t>
         </is>
       </c>
       <c r="J113" s="2" t="n">
-        <v>503404000</v>
+        <v>232911000</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="3" t="n">
-        <v>46272</v>
+        <v>46266</v>
       </c>
       <c r="B114" t="n">
         <v>206</v>
       </c>
       <c r="C114" s="2" t="n">
-        <v>25953000</v>
+        <v>8251000</v>
       </c>
       <c r="D114" s="2" t="n"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Durdona Dori-Darmon MChJ</t>
+          <t>Andijon Logistik MChJ</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>306318030</t>
+          <t>290703257</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>20208000554383246001</t>
+          <t>20208000232420108001</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №192/26, QQS bilan</t>
+          <t>Transport xizmatlari uchun to'lov, shartn. №257/26</t>
         </is>
       </c>
       <c r="J114" s="2" t="n">
-        <v>477451000</v>
+        <v>224660000</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="3" t="n">
-        <v>46272</v>
+        <v>46266</v>
       </c>
       <c r="B115" t="n">
         <v>207</v>
       </c>
       <c r="C115" s="2" t="n">
-        <v>30245000</v>
+        <v>24073000</v>
       </c>
       <c r="D115" s="2" t="n"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Shahrisabz Avto Ehtiyot AJ</t>
+          <t>Nihol Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>362972200</t>
+          <t>256622789</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>20208000902223626001</t>
+          <t>20208000888983796001</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartn. №107/26, QQS bilan</t>
+          <t>Materiallar uchun oldindan to'lov, shartn. №27/26</t>
         </is>
       </c>
       <c r="J115" s="2" t="n">
-        <v>447206000</v>
+        <v>200587000</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="3" t="n">
-        <v>46272</v>
+        <v>46267</v>
       </c>
       <c r="B116" t="n">
         <v>208</v>
       </c>
-      <c r="C116" s="2" t="n">
-        <v>36764000</v>
-      </c>
-      <c r="D116" s="2" t="n"/>
+      <c r="C116" s="2" t="n"/>
+      <c r="D116" s="2" t="n">
+        <v>18143000</v>
+      </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Yangi Asr Bank</t>
+          <t>Ziyo Yog'och MChJ</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>312245313</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000098017876001</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Ish haqi to'lovi avgust 2026 (plastik kartalarga)</t>
+          <t>Mahsulot uchun to'lov, shartnoma №113/26, QQS 12%</t>
         </is>
       </c>
       <c r="J116" s="2" t="n">
-        <v>410442000</v>
+        <v>218730000</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="3" t="n">
-        <v>46273</v>
+        <v>46268</v>
       </c>
       <c r="B117" t="n">
         <v>209</v>
       </c>
-      <c r="C117" s="2" t="n"/>
-      <c r="D117" s="2" t="n">
-        <v>7346000</v>
-      </c>
+      <c r="C117" s="2" t="n">
+        <v>10129000</v>
+      </c>
+      <c r="D117" s="2" t="n"/>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Gulshan Yog' Zavodi MChJ</t>
+          <t>Nurafshon Moy MChJ</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>317122453</t>
+          <t>331803035</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>20208000340980178001</t>
+          <t>20208000438324655001</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №277/26, QQS 12%</t>
+          <t>Tovarlar uchun to'lov h/f №2614</t>
         </is>
       </c>
       <c r="J117" s="2" t="n">
-        <v>417788000</v>
+        <v>208601000</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="3" t="n">
-        <v>46273</v>
+        <v>46269</v>
       </c>
       <c r="B118" t="n">
         <v>210</v>
       </c>
-      <c r="C118" s="2" t="n">
-        <v>36692000</v>
-      </c>
-      <c r="D118" s="2" t="n"/>
+      <c r="C118" s="2" t="n"/>
+      <c r="D118" s="2" t="n">
+        <v>12873000</v>
+      </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Durdona Dori-Darmon MChJ</t>
+          <t>Xiva Polimer AJ</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>306318030</t>
+          <t>257873684</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>20208000554383246001</t>
+          <t>20208000626499181001</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartn. №227/26</t>
+          <t>Shartnoma №254/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J118" s="2" t="n">
-        <v>381096000</v>
+        <v>221474000</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="3" t="n">
-        <v>46274</v>
+        <v>46269</v>
       </c>
       <c r="B119" t="n">
         <v>211</v>
       </c>
       <c r="C119" s="2" t="n"/>
       <c r="D119" s="2" t="n">
-        <v>8398000</v>
+        <v>9545000</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Jizzax Non AJ</t>
+          <t>Xiva Polimer AJ</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>384578736</t>
+          <t>257873684</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>20208000406264991001</t>
+          <t>20208000626499181001</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №5371</t>
+          <t>Tovar uchun to'lov, hisob-faktura №5727 04.09.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J119" s="2" t="n">
-        <v>389494000</v>
+        <v>231019000</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="3" t="n">
-        <v>46274</v>
+        <v>46269</v>
       </c>
       <c r="B120" t="n">
         <v>212</v>
       </c>
       <c r="C120" s="2" t="n">
-        <v>11420000</v>
+        <v>36764000</v>
       </c>
       <c r="D120" s="2" t="n"/>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Omad Moy AJ</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>319688973</t>
+          <t>Yangi Asr Bank</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>20208000890097668001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №5297</t>
+          <t>Ish haqi to'lovi avgust 2026 (plastik kartalarga)</t>
         </is>
       </c>
       <c r="J120" s="2" t="n">
-        <v>378074000</v>
+        <v>194255000</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="3" t="n">
-        <v>46275</v>
+        <v>46272</v>
       </c>
       <c r="B121" t="n">
         <v>213</v>
       </c>
       <c r="C121" s="2" t="n"/>
       <c r="D121" s="2" t="n">
-        <v>18846000</v>
+        <v>13867000</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Mehnat Poligraf MChJ</t>
+          <t>Xiva Polimer AJ</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>224230666</t>
+          <t>257873684</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>20208000074661545001</t>
+          <t>20208000626499181001</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Shartnoma №124/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за товар по счет-фактуре №5372 от 07.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J121" s="2" t="n">
-        <v>396920000</v>
+        <v>208122000</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="3" t="n">
-        <v>46275</v>
+        <v>46272</v>
       </c>
       <c r="B122" t="n">
         <v>214</v>
       </c>
       <c r="C122" s="2" t="n">
-        <v>41957000</v>
+        <v>8151000</v>
       </c>
       <c r="D122" s="2" t="n"/>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Durdona Dori-Darmon MChJ</t>
+          <t>Nurafshon Logistik XK</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>306318030</t>
+          <t>267357497</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>20208000554383246001</t>
+          <t>20208000958282772001</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartn. №163/26</t>
+          <t>Tovarlar uchun to'lov h/f №5072</t>
         </is>
       </c>
       <c r="J122" s="2" t="n">
-        <v>354963000</v>
+        <v>199971000</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="3" t="n">
-        <v>46276</v>
+        <v>46272</v>
       </c>
       <c r="B123" t="n">
         <v>215</v>
       </c>
-      <c r="C123" s="2" t="n"/>
-      <c r="D123" s="2" t="n">
-        <v>9772000</v>
-      </c>
+      <c r="C123" s="2" t="n">
+        <v>11848000</v>
+      </c>
+      <c r="D123" s="2" t="n"/>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Jizzax Non AJ</t>
+          <t>Andijon Logistik MChJ</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>384578736</t>
+          <t>290703257</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>20208000406264991001</t>
+          <t>20208000232420108001</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №216/26, QQS 12%</t>
+          <t>Tovarlar uchun to'lov h/f №1735</t>
         </is>
       </c>
       <c r="J123" s="2" t="n">
-        <v>364735000</v>
+        <v>188123000</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="3" t="n">
-        <v>46276</v>
+        <v>46274</v>
       </c>
       <c r="B124" t="n">
         <v>216</v>
       </c>
       <c r="C124" s="2" t="n"/>
       <c r="D124" s="2" t="n">
-        <v>2861000</v>
+        <v>15120000</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Bog'ishamol Oziq-ovqat Savdo AJ</t>
+          <t>Xiva Polimer AJ</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>228782815</t>
+          <t>257873684</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>20208000977315442001</t>
+          <t>20208000626499181001</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -5171,117 +5171,117 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №228/26, QQS 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №5371</t>
         </is>
       </c>
       <c r="J124" s="2" t="n">
-        <v>367596000</v>
+        <v>203243000</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="3" t="n">
-        <v>46276</v>
+        <v>46274</v>
       </c>
       <c r="B125" t="n">
         <v>217</v>
       </c>
       <c r="C125" s="2" t="n"/>
       <c r="D125" s="2" t="n">
-        <v>2842000</v>
+        <v>4529000</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Jizzax Non AJ</t>
+          <t>Xiva Polimer AJ</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>384578736</t>
+          <t>257873684</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>20208000406264991001</t>
+          <t>20208000626499181001</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №6775 за поставленный товар</t>
+          <t>Shartnoma №294/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J125" s="2" t="n">
-        <v>370438000</v>
+        <v>207772000</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="3" t="n">
-        <v>46276</v>
+        <v>46274</v>
       </c>
       <c r="B126" t="n">
         <v>218</v>
       </c>
       <c r="C126" s="2" t="n">
-        <v>21754000</v>
+        <v>3187000</v>
       </c>
       <c r="D126" s="2" t="n"/>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Nihol Meva-Sabzavot MChJ</t>
+          <t>Saodat Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>264566227</t>
+          <t>384857731</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>20208000988889837001</t>
+          <t>20208000469248688001</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №9721</t>
+          <t>IJARA HAQI SENTYABR OYI UCHUN, SHARTNOMA №95/25</t>
         </is>
       </c>
       <c r="J126" s="2" t="n">
-        <v>348684000</v>
+        <v>204585000</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="3" t="n">
-        <v>46279</v>
+        <v>46275</v>
       </c>
       <c r="B127" t="n">
         <v>219</v>
       </c>
       <c r="C127" s="2" t="n"/>
       <c r="D127" s="2" t="n">
-        <v>23992000</v>
+        <v>202940000</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Jizzax Non AJ</t>
+          <t>Lazzat Savdo MChJ</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>384578736</t>
+          <t>223066690</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>20208000406264991001</t>
+          <t>20208000466154582001</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -5291,171 +5291,171 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Shartnoma №133/26 bo'yicha oldindan to'lov</t>
+          <t>Shartnoma №124/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J127" s="2" t="n">
-        <v>372676000</v>
+        <v>407525000</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="3" t="n">
-        <v>46279</v>
+        <v>46276</v>
       </c>
       <c r="B128" t="n">
         <v>220</v>
       </c>
-      <c r="C128" s="2" t="n">
-        <v>5013000</v>
-      </c>
-      <c r="D128" s="2" t="n"/>
+      <c r="C128" s="2" t="n"/>
+      <c r="D128" s="2" t="n">
+        <v>16045000</v>
+      </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Xiva Polimer AJ</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>257873684</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000626499181001</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Социальный налог за август 2026 г.</t>
+          <t>Mahsulot uchun to'lov, shartn. №216/26, QQS 12%</t>
         </is>
       </c>
       <c r="J128" s="2" t="n">
-        <v>367663000</v>
+        <v>423570000</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="3" t="n">
-        <v>46279</v>
+        <v>46276</v>
       </c>
       <c r="B129" t="n">
         <v>221</v>
       </c>
-      <c r="C129" s="2" t="n">
-        <v>5013000</v>
-      </c>
-      <c r="D129" s="2" t="n"/>
+      <c r="C129" s="2" t="n"/>
+      <c r="D129" s="2" t="n">
+        <v>12396000</v>
+      </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Xiva Polimer AJ</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>257873684</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000626499181001</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Jismoniy shaxslar daromad solig'i avgust 2026</t>
+          <t>Оплата по с/ф №6775 за поставленный товар</t>
         </is>
       </c>
       <c r="J129" s="2" t="n">
-        <v>362650000</v>
+        <v>435966000</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="3" t="n">
-        <v>46279</v>
+        <v>46276</v>
       </c>
       <c r="B130" t="n">
         <v>222</v>
       </c>
-      <c r="C130" s="2" t="n">
-        <v>7049000</v>
-      </c>
-      <c r="D130" s="2" t="n"/>
+      <c r="C130" s="2" t="n"/>
+      <c r="D130" s="2" t="n">
+        <v>5474000</v>
+      </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Durdona Dori-Darmon MChJ</t>
+          <t>Qo'qon Agro Servis MChJ</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>306318030</t>
+          <t>378281519</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>20208000554383246001</t>
+          <t>20208000731544252001</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №3913</t>
+          <t>Mahsulot uchun to'lov, shartn. №228/26, QQS 12%</t>
         </is>
       </c>
       <c r="J130" s="2" t="n">
-        <v>355601000</v>
+        <v>441440000</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="3" t="n">
-        <v>46279</v>
+        <v>46276</v>
       </c>
       <c r="B131" t="n">
         <v>223</v>
       </c>
-      <c r="C131" s="2" t="n">
-        <v>7551000</v>
-      </c>
-      <c r="D131" s="2" t="n"/>
+      <c r="C131" s="2" t="n"/>
+      <c r="D131" s="2" t="n">
+        <v>3124000</v>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Durdona Dori-Darmon MChJ</t>
+          <t>Lazzat Savdo MChJ</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>306318030</t>
+          <t>223066690</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>20208000554383246001</t>
+          <t>20208000466154582001</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №197/26</t>
+          <t>Оплата по счет-фактуре№7066 за поставленный товар</t>
         </is>
       </c>
       <c r="J131" s="2" t="n">
-        <v>348050000</v>
+        <v>444564000</v>
       </c>
     </row>
     <row r="132">
@@ -5465,383 +5465,383 @@
       <c r="B132" t="n">
         <v>224</v>
       </c>
-      <c r="C132" s="2" t="n">
-        <v>11152000</v>
-      </c>
-      <c r="D132" s="2" t="n"/>
+      <c r="C132" s="2" t="n"/>
+      <c r="D132" s="2" t="n">
+        <v>16772000</v>
+      </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Durdona Dori-Darmon MChJ</t>
+          <t>Lazzat Savdo MChJ</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>306318030</t>
+          <t>223066690</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>20208000554383246001</t>
+          <t>20208000466154582001</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №28/26</t>
+          <t>Mahsulot uchun to'lov, shartnoma №223/26, QQS 12%</t>
         </is>
       </c>
       <c r="J132" s="2" t="n">
-        <v>336898000</v>
+        <v>461336000</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="3" t="n">
-        <v>46280</v>
+        <v>46279</v>
       </c>
       <c r="B133" t="n">
         <v>225</v>
       </c>
       <c r="C133" s="2" t="n"/>
       <c r="D133" s="2" t="n">
-        <v>4780000</v>
+        <v>16337000</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Jizzax Non AJ</t>
+          <t>Xiva Polimer AJ</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>384578736</t>
+          <t>257873684</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>20208000406264991001</t>
+          <t>20208000626499181001</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №5357</t>
+          <t>Tovar uchun to'lov, hisob-faktura №6375 14.09.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J133" s="2" t="n">
-        <v>341678000</v>
+        <v>477673000</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="3" t="n">
-        <v>46280</v>
+        <v>46279</v>
       </c>
       <c r="B134" t="n">
         <v>226</v>
       </c>
       <c r="C134" s="2" t="n">
-        <v>34584000</v>
+        <v>9611000</v>
       </c>
       <c r="D134" s="2" t="n"/>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Nihol Meva-Sabzavot MChJ</t>
+          <t>Andijon Logistik MChJ</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>264566227</t>
+          <t>290703257</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>20208000988889837001</t>
+          <t>20208000232420108001</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №214/26</t>
+          <t>Tovarlar uchun to'lov h/f №6076</t>
         </is>
       </c>
       <c r="J134" s="2" t="n">
-        <v>307094000</v>
+        <v>468062000</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="3" t="n">
-        <v>46286</v>
+        <v>46280</v>
       </c>
       <c r="B135" t="n">
         <v>227</v>
       </c>
-      <c r="C135" s="2" t="n">
-        <v>15851000</v>
-      </c>
-      <c r="D135" s="2" t="n"/>
+      <c r="C135" s="2" t="n"/>
+      <c r="D135" s="2" t="n">
+        <v>5190000</v>
+      </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Qarshi Mehmonxona MChJ</t>
+          <t>Xiva Polimer AJ</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>250023319</t>
+          <t>257873684</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>20208000275405590001</t>
+          <t>20208000626499181001</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartn. №214/26</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №5357</t>
         </is>
       </c>
       <c r="J135" s="2" t="n">
-        <v>291243000</v>
+        <v>473252000</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="3" t="n">
-        <v>46286</v>
+        <v>46280</v>
       </c>
       <c r="B136" t="n">
         <v>228</v>
       </c>
       <c r="C136" s="2" t="n">
-        <v>26963000</v>
+        <v>5013000</v>
       </c>
       <c r="D136" s="2" t="n"/>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Durdona Dori-Darmon MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>306318030</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>20208000554383246001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №121/26, QQS bilan</t>
+          <t>Avgust oyi uchun ijtimoiy soliq</t>
         </is>
       </c>
       <c r="J136" s="2" t="n">
-        <v>264280000</v>
+        <v>468239000</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="3" t="n">
-        <v>46287</v>
+        <v>46280</v>
       </c>
       <c r="B137" t="n">
         <v>229</v>
       </c>
-      <c r="C137" s="2" t="n"/>
-      <c r="D137" s="2" t="n">
-        <v>20538000</v>
-      </c>
+      <c r="C137" s="2" t="n">
+        <v>5013000</v>
+      </c>
+      <c r="D137" s="2" t="n"/>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Mehnat Poligraf MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>224230666</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>20208000074661545001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №223/26, QQS 12%</t>
+          <t>Jismoniy shaxslar daromad solig'i avgust 2026</t>
         </is>
       </c>
       <c r="J137" s="2" t="n">
-        <v>284818000</v>
+        <v>463226000</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="3" t="n">
-        <v>46287</v>
+        <v>46280</v>
       </c>
       <c r="B138" t="n">
         <v>230</v>
       </c>
       <c r="C138" s="2" t="n">
-        <v>5284000</v>
+        <v>43386000</v>
       </c>
       <c r="D138" s="2" t="n"/>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Nurafshon Moy MChJ</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>331803035</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000438324655001</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Qo'shilgan qiymat solig'i avgust oyi</t>
+          <t>Предоплата за материалы по дог. №27/26</t>
         </is>
       </c>
       <c r="J138" s="2" t="n">
-        <v>279534000</v>
+        <v>419840000</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="3" t="n">
-        <v>46287</v>
+        <v>46281</v>
       </c>
       <c r="B139" t="n">
         <v>231</v>
       </c>
       <c r="C139" s="2" t="n">
-        <v>11954000</v>
+        <v>13746000</v>
       </c>
       <c r="D139" s="2" t="n"/>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Qarshi Mehmonxona MChJ</t>
+          <t>Qarshi Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>250023319</t>
+          <t>242558726</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>20208000275405590001</t>
+          <t>20208000685861603001</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №78/26</t>
+          <t>Materiallar uchun oldindan to'lov, shartn. №194/26</t>
         </is>
       </c>
       <c r="J139" s="2" t="n">
-        <v>267580000</v>
+        <v>406094000</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="3" t="n">
-        <v>46287</v>
+        <v>46282</v>
       </c>
       <c r="B140" t="n">
         <v>232</v>
       </c>
-      <c r="C140" s="2" t="n">
-        <v>13390000</v>
-      </c>
-      <c r="D140" s="2" t="n"/>
+      <c r="C140" s="2" t="n"/>
+      <c r="D140" s="2" t="n">
+        <v>8597000</v>
+      </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Kamalak Farm Savdo MChJ</t>
+          <t>Xiva Polimer AJ</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>297349587</t>
+          <t>257873684</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>20208000889492055001</t>
+          <t>20208000626499181001</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №105/26</t>
+          <t>Mahsulot uchun to'lov, shartnoma №211/26, QQS 12%</t>
         </is>
       </c>
       <c r="J140" s="2" t="n">
-        <v>254190000</v>
+        <v>414691000</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="3" t="n">
-        <v>46288</v>
+        <v>46286</v>
       </c>
       <c r="B141" t="n">
         <v>233</v>
       </c>
       <c r="C141" s="2" t="n"/>
       <c r="D141" s="2" t="n">
-        <v>3533000</v>
+        <v>6454000</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Jizzax Non AJ</t>
+          <t>Lazzat Savdo MChJ</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>384578736</t>
+          <t>223066690</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>20208000406264991001</t>
+          <t>20208000466154582001</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -5851,312 +5851,317 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Shartnoma №47/26 bo'yicha oldindan to'lov</t>
+          <t>Mahsulot uchun to'lov, shartn. №288/26, QQS 12%</t>
         </is>
       </c>
       <c r="J141" s="2" t="n">
-        <v>257723000</v>
+        <v>421145000</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="3" t="n">
-        <v>46288</v>
+        <v>46286</v>
       </c>
       <c r="B142" t="n">
         <v>234</v>
       </c>
       <c r="C142" s="2" t="n"/>
       <c r="D142" s="2" t="n">
-        <v>3493000</v>
+        <v>3356000</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Jizzax Non AJ</t>
+          <t>Xiva Polimer AJ</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>384578736</t>
+          <t>257873684</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>20208000406264991001</t>
+          <t>20208000626499181001</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №633 23.09.2026, QQS bilan</t>
+          <t>Mahsulot uchun to'lov, shartnoma №220/26, QQS 12%</t>
         </is>
       </c>
       <c r="J142" s="2" t="n">
-        <v>261216000</v>
+        <v>424501000</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="3" t="n">
-        <v>46288</v>
+        <v>46286</v>
       </c>
       <c r="B143" t="n">
         <v>235</v>
       </c>
-      <c r="C143" s="2" t="n">
-        <v>7541000</v>
-      </c>
-      <c r="D143" s="2" t="n"/>
+      <c r="C143" s="2" t="n"/>
+      <c r="D143" s="2" t="n">
+        <v>3194000</v>
+      </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Durdona Dori-Darmon MChJ</t>
+          <t>Xiva Polimer AJ</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>306318030</t>
+          <t>257873684</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>20208000554383246001</t>
+          <t>20208000626499181001</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №297/26 от 23.09.2026, НДС 12%</t>
+          <t>Shartnoma №255/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J143" s="2" t="n">
-        <v>253675000</v>
+        <v>427695000</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="3" t="n">
-        <v>46289</v>
+        <v>46286</v>
       </c>
       <c r="B144" t="n">
         <v>236</v>
       </c>
-      <c r="C144" s="2" t="n"/>
-      <c r="D144" s="2" t="n">
-        <v>8898000</v>
-      </c>
+      <c r="C144" s="2" t="n">
+        <v>33241000</v>
+      </c>
+      <c r="D144" s="2" t="n"/>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Jizzax Non AJ</t>
+          <t>Andijon Logistik MChJ</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>384578736</t>
+          <t>290703257</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>20208000406264991001</t>
+          <t>20208000232420108001</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №173/26, QQS 12%</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №199/26, QQS bilan</t>
         </is>
       </c>
       <c r="J144" s="2" t="n">
-        <v>262573000</v>
+        <v>394454000</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="3" t="n">
-        <v>46289</v>
+        <v>46286</v>
       </c>
       <c r="B145" t="n">
         <v>237</v>
       </c>
-      <c r="C145" s="2" t="n"/>
-      <c r="D145" s="2" t="n">
-        <v>5352000</v>
-      </c>
+      <c r="C145" s="2" t="n">
+        <v>76634000</v>
+      </c>
+      <c r="D145" s="2" t="n"/>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Olmaliq Yog'och MChJ</t>
+          <t>Andijon Logistik MChJ</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>271673574</t>
+          <t>290703257</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>20208000779582827001</t>
+          <t>20208000232420108001</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №4731</t>
+          <t>Materiallar uchun oldindan to'lov, shartn. №170/26</t>
         </is>
       </c>
       <c r="J145" s="2" t="n">
-        <v>267925000</v>
+        <v>317820000</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="3" t="n">
-        <v>46290</v>
+        <v>46287</v>
       </c>
       <c r="B146" t="n">
         <v>238</v>
       </c>
-      <c r="C146" s="2" t="n"/>
-      <c r="D146" s="2" t="n">
-        <v>5806000</v>
-      </c>
+      <c r="C146" s="2" t="n">
+        <v>5339000</v>
+      </c>
+      <c r="D146" s="2" t="n"/>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Jizzax Non AJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>384578736</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>20208000406264991001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №5159</t>
+          <t>НДС за август 2026 г.</t>
         </is>
       </c>
       <c r="J146" s="2" t="n">
-        <v>273731000</v>
+        <v>312481000</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="3" t="n">
-        <v>46290</v>
+        <v>46288</v>
       </c>
       <c r="B147" t="n">
         <v>239</v>
       </c>
-      <c r="C147" s="2" t="n">
-        <v>45100000</v>
-      </c>
-      <c r="D147" s="2" t="n"/>
+      <c r="C147" s="2" t="n"/>
+      <c r="D147" s="2" t="n">
+        <v>16863000</v>
+      </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-5488)</t>
+          <t>Xiva Polimer AJ</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>257873684</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>16307000345325813417</t>
+          <t>20208000626499181001</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-5488 bo'yicha navbatdagi to'lov (09.2026)</t>
+          <t>Shartnoma №47/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J147" s="2" t="n">
-        <v>228631000</v>
+        <v>329344000</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="3" t="n">
-        <v>46293</v>
+        <v>46288</v>
       </c>
       <c r="B148" t="n">
         <v>240</v>
       </c>
       <c r="C148" s="2" t="n">
-        <v>1992000</v>
+        <v>43018000</v>
       </c>
       <c r="D148" s="2" t="n"/>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Andijon Logistik MChJ</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>290703257</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>20208000474560325001</t>
+          <t>20208000232420108001</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Elektr energiyasi uchun to'lov sentyabr</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №205/26</t>
         </is>
       </c>
       <c r="J148" s="2" t="n">
-        <v>226639000</v>
+        <v>286326000</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="3" t="n">
-        <v>46295</v>
+        <v>46289</v>
       </c>
       <c r="B149" t="n">
         <v>241</v>
       </c>
       <c r="C149" s="2" t="n"/>
       <c r="D149" s="2" t="n">
-        <v>34454000</v>
+        <v>14108000</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Jizzax Non AJ</t>
+          <t>Sarbon Agro AJ</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>384578736</t>
+          <t>230167378</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>20208000406264991001</t>
+          <t>20208000670005672001</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -6166,111 +6171,466 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №132/26, QQS 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №4731</t>
         </is>
       </c>
       <c r="J149" s="2" t="n">
-        <v>261093000</v>
+        <v>300434000</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="3" t="n">
-        <v>46295</v>
+        <v>46289</v>
       </c>
       <c r="B150" t="n">
         <v>242</v>
       </c>
       <c r="C150" s="2" t="n">
-        <v>300000</v>
+        <v>13187000</v>
       </c>
       <c r="D150" s="2" t="n"/>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Yangi Asr Bank</t>
+          <t>Qo'qon Sut Mahsulotlari MChJ</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>297220069</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000222362626001</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Bank xizmati uchun komissiya</t>
+          <t>Tovarlar uchun to'lov h/f №3511</t>
         </is>
       </c>
       <c r="J150" s="2" t="n">
-        <v>260793000</v>
+        <v>287247000</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="3" t="n">
-        <v>46295</v>
+        <v>46290</v>
       </c>
       <c r="B151" t="n">
         <v>243</v>
       </c>
-      <c r="C151" s="2" t="n">
-        <v>6793000</v>
-      </c>
-      <c r="D151" s="2" t="n"/>
+      <c r="C151" s="2" t="n"/>
+      <c r="D151" s="2" t="n">
+        <v>10018000</v>
+      </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Namangan Sut Mahsulotlari MChJ</t>
+          <t>Xiva Polimer AJ</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>231235630</t>
+          <t>257873684</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>20208000785568112001</t>
+          <t>20208000626499181001</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>Shartnoma №134/26 bo'yicha oldindan to'lov</t>
+        </is>
+      </c>
+      <c r="J151" s="2" t="n">
+        <v>297265000</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="3" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B152" t="n">
+        <v>244</v>
+      </c>
+      <c r="C152" s="2" t="n"/>
+      <c r="D152" s="2" t="n">
+        <v>6409000</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Xiva Polimer AJ</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>257873684</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>20208000626499181001</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>Yetkazilgan tovar uchun to'lov h/f №5159</t>
+        </is>
+      </c>
+      <c r="J152" s="2" t="n">
+        <v>303674000</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="3" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B153" t="n">
+        <v>245</v>
+      </c>
+      <c r="C153" s="2" t="n">
+        <v>45100000</v>
+      </c>
+      <c r="D153" s="2" t="n"/>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-5488)</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>16307000345325813417</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>01089</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>Kredit shartnomasi L-2025-5488 bo'yicha navbatdagi to'lov (09.2026)</t>
+        </is>
+      </c>
+      <c r="J153" s="2" t="n">
+        <v>258574000</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B154" t="n">
+        <v>246</v>
+      </c>
+      <c r="C154" s="2" t="n"/>
+      <c r="D154" s="2" t="n">
+        <v>4033000</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Ziyo Yog'och MChJ</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>312245313</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>20208000098017876001</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
           <t>00987</t>
         </is>
       </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>Xom ashyo uchun to'lov, shartn. №244/26, QQS bilan</t>
-        </is>
-      </c>
-      <c r="J151" s="2" t="n">
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>Yetkazilgan tovar uchun to'lov h/f №8141</t>
+        </is>
+      </c>
+      <c r="J154" s="2" t="n">
+        <v>262607000</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B155" t="n">
+        <v>247</v>
+      </c>
+      <c r="C155" s="2" t="n">
+        <v>1992000</v>
+      </c>
+      <c r="D155" s="2" t="n"/>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Hududiy elektr tarmoqlari AJ</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>200933985</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>20208000585196889001</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>Оплата за электроэнергию согласно счету</t>
+        </is>
+      </c>
+      <c r="J155" s="2" t="n">
+        <v>260615000</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B156" t="n">
+        <v>248</v>
+      </c>
+      <c r="C156" s="2" t="n">
+        <v>10624000</v>
+      </c>
+      <c r="D156" s="2" t="n"/>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Andijon Logistik MChJ</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>290703257</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>20208000232420108001</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>Xom ashyo uchun to'lov, shartnoma №15/26, QQS bilan</t>
+        </is>
+      </c>
+      <c r="J156" s="2" t="n">
+        <v>249991000</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B157" t="n">
+        <v>249</v>
+      </c>
+      <c r="C157" s="2" t="n">
+        <v>15214000</v>
+      </c>
+      <c r="D157" s="2" t="n"/>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Andijon Logistik MChJ</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>290703257</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>20208000232420108001</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>Оплата за транспортные услуги по дог. №282/26</t>
+        </is>
+      </c>
+      <c r="J157" s="2" t="n">
+        <v>234777000</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="3" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B158" t="n">
+        <v>250</v>
+      </c>
+      <c r="C158" s="2" t="n"/>
+      <c r="D158" s="2" t="n">
+        <v>10333000</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Xiva Polimer AJ</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>257873684</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>20208000626499181001</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>Mahsulot uchun to'lov, shartnoma №132/26, QQS 12%</t>
+        </is>
+      </c>
+      <c r="J158" s="2" t="n">
+        <v>245110000</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="3" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B159" t="n">
+        <v>251</v>
+      </c>
+      <c r="C159" s="2" t="n"/>
+      <c r="D159" s="2" t="n">
+        <v>9190000</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Lazzat Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>223066690</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>20208000466154582001</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>01089</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>Оплата по счет-фактуре №7692 за поставленный товар</t>
+        </is>
+      </c>
+      <c r="J159" s="2" t="n">
+        <v>254300000</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="3" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B160" t="n">
+        <v>252</v>
+      </c>
+      <c r="C160" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D160" s="2" t="n"/>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Yangi Asr Bank</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>45994000900000001001</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>01089</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>Bank xizmati uchun komissiya</t>
+        </is>
+      </c>
+      <c r="J160" s="2" t="n">
         <v>254000000</v>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
+    <row r="161">
+      <c r="A161" t="inlineStr">
         <is>
           <t>Итого обороты:</t>
         </is>
       </c>
-      <c r="C152" s="4" t="n">
-        <v>1371625000</v>
-      </c>
-      <c r="D152" s="4" t="n">
-        <v>1403725000</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
+      <c r="C161" s="4" t="n">
+        <v>1351532000</v>
+      </c>
+      <c r="D161" s="4" t="n">
+        <v>1383632000</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
         <is>
           <t>Исходящий остаток на 30.09.2026:</t>
         </is>
       </c>
-      <c r="C153" s="4" t="n">
+      <c r="C162" s="4" t="n">
         <v>254000000</v>
       </c>
-      <c r="D153" s="4" t="n"/>
+      <c r="D162" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
